--- a/mainWidget/mainWidget/src/database/计算模型-慢速烤燃试验.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-慢速烤燃试验.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45541376-A4FE-4656-920C-858597037B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5ED57F-91CE-472D-9253-84BD3A3382BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="1043">
   <si>
     <t>序号</t>
   </si>
@@ -248,625 +248,3077 @@
   </si>
   <si>
     <t>-3.2942</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.5744</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.293</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6253</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-54.1842</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-58.1775</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-54.1829</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6246</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6958</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-60.995</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.574</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-34.821</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-65.5512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-60.9937</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6954</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.7005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-61.0305</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-65.5956</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-61.0289</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6994</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6295</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-54.2359</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-58.2405</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-54.2343</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6284</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.2952</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.6262</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.2932</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.6255</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-34.885</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0505</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0504</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0546</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0719</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0533</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.072</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0548</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0534</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1124</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0915</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0515</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.126</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0913</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0514</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1259</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1035</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1036</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0122</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0131</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0204</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0221</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0249</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0203</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2542</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6321</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.608</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2543</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2672</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0869</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0795</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2554</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2552</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.255</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2534</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2532</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2668</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.085</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0773</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.254</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6307</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0094</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0148</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0046</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0187</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0161</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0066</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0229</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0227</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0379</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0385</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0059</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0429</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0437</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0438</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0414</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2398</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0038</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9948</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2793</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0687</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0586</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9929</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0413</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0686</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0585</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0444</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1141</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0433</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1308</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1193</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1309</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1194</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1143</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1031</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2245</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.919</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.7966</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1836</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.0459</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.89</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1834</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.0473</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.8921</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.0474</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2243</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.9193</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.7973</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2781</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2095</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9884</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.993</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9911</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0051</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9901</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9871</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-28.8425-0.0006*B+0.0000*C+0.0836*D+0.0071*E-0.0017*F+0.0000*G+0.8305*H-0.0131*I+0.0404*J-0.0702*K+0.7883*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-28.8425</t>
+  </si>
+  <si>
+    <t>-0.0006</t>
+  </si>
+  <si>
+    <t>0.0000</t>
+  </si>
+  <si>
+    <t>0.0836</t>
+  </si>
+  <si>
+    <t>0.0071</t>
+  </si>
+  <si>
+    <t>-0.0017</t>
+  </si>
+  <si>
+    <t>0.8305</t>
+  </si>
+  <si>
+    <t>-0.0131</t>
+  </si>
+  <si>
+    <t>0.0404</t>
+  </si>
+  <si>
+    <t>-0.0702</t>
+  </si>
+  <si>
+    <t>0.7883</t>
+  </si>
+  <si>
+    <t>1.0858</t>
+  </si>
+  <si>
+    <t>-27.8387-0.0005*B+0.0000*C+0.0860*D+0.0113*E-0.0020*F+0.0000*G+0.8936*H-0.0128*I+0.0233*J-0.1400*K+1.3599*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-27.8387</t>
+  </si>
+  <si>
+    <t>-0.0005</t>
+  </si>
+  <si>
+    <t>0.0860</t>
+  </si>
+  <si>
+    <t>0.0113</t>
+  </si>
+  <si>
+    <t>-0.0020</t>
+  </si>
+  <si>
+    <t>0.8936</t>
+  </si>
+  <si>
+    <t>-0.0128</t>
+  </si>
+  <si>
+    <t>0.0233</t>
+  </si>
+  <si>
+    <t>-0.1400</t>
+  </si>
+  <si>
+    <t>1.3599</t>
+  </si>
+  <si>
+    <t>-36.2609-0.0002*B+0.0000*C+0.0554*D+0.0111*E-0.0019*F+0.0000*G+0.8724*H-0.0168*I+0.0251*J-0.0767*K+1.6985*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-36.2609</t>
+  </si>
+  <si>
+    <t>-0.0002</t>
+  </si>
+  <si>
+    <t>0.0554</t>
+  </si>
+  <si>
+    <t>0.0111</t>
+  </si>
+  <si>
+    <t>-0.0019</t>
+  </si>
+  <si>
+    <t>0.8724</t>
+  </si>
+  <si>
+    <t>-0.0168</t>
+  </si>
+  <si>
+    <t>0.0251</t>
+  </si>
+  <si>
+    <t>-0.0767</t>
+  </si>
+  <si>
+    <t>1.6985</t>
+  </si>
+  <si>
+    <t>-44.0992-0.0002*B+0.0000*C+0.0627*D+0.0169*E-0.0020*F+0.0000*G+0.3950*H-0.0112*I+0.0105*J-0.0722*K+0.7214*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-44.0992</t>
+  </si>
+  <si>
+    <t>0.0627</t>
+  </si>
+  <si>
+    <t>0.0169</t>
+  </si>
+  <si>
+    <t>0.3950</t>
+  </si>
+  <si>
+    <t>-0.0112</t>
+  </si>
+  <si>
+    <t>0.0105</t>
+  </si>
+  <si>
+    <t>-0.0722</t>
+  </si>
+  <si>
+    <t>0.7214</t>
+  </si>
+  <si>
+    <t>-16.6450-0.0004*B+0.0000*C+0.0824*D+0.0126*E-0.0021*F+0.0000*G+0.6953*H-0.0079*I+0.0347*J-0.0642*K+1.3586*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-16.6450</t>
+  </si>
+  <si>
+    <t>-0.0004</t>
+  </si>
+  <si>
+    <t>0.0824</t>
+  </si>
+  <si>
+    <t>0.0126</t>
+  </si>
+  <si>
+    <t>-0.0021</t>
+  </si>
+  <si>
+    <t>0.6953</t>
+  </si>
+  <si>
+    <t>-0.0079</t>
+  </si>
+  <si>
+    <t>0.0347</t>
+  </si>
+  <si>
+    <t>-0.0642</t>
+  </si>
+  <si>
+    <t>1.3586</t>
+  </si>
+  <si>
+    <t>-41.7933-0.0003*B+0.0000*C+0.0554*D+0.0086*E-0.0025*F+0.0000*G+0.3299*H-0.0051*I+0.0236*J-0.1087*K+0.8199*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-41.7933</t>
+  </si>
+  <si>
+    <t>-0.0003</t>
+  </si>
+  <si>
+    <t>0.0086</t>
+  </si>
+  <si>
+    <t>-0.0025</t>
+  </si>
+  <si>
+    <t>0.3299</t>
+  </si>
+  <si>
+    <t>-0.0051</t>
+  </si>
+  <si>
+    <t>0.0236</t>
+  </si>
+  <si>
+    <t>-0.1087</t>
+  </si>
+  <si>
+    <t>0.8199</t>
+  </si>
+  <si>
+    <t>-23.6830-0.0005*B+0.0000*C+0.0905*D+0.0105*E-0.0023*F+0.0000*G+1.1660*H-0.0092*I+0.0199*J-0.0553*K+1.8797*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-23.6830</t>
+  </si>
+  <si>
+    <t>0.0905</t>
+  </si>
+  <si>
+    <t>-0.0023</t>
+  </si>
+  <si>
+    <t>1.1660</t>
+  </si>
+  <si>
+    <t>-0.0092</t>
+  </si>
+  <si>
+    <t>0.0199</t>
+  </si>
+  <si>
+    <t>-0.0553</t>
+  </si>
+  <si>
+    <t>1.8797</t>
+  </si>
+  <si>
+    <t>-18.9758-0.0005*B+0.0000*C+0.0780*D+0.0144*E-0.0025*F+0.0000*G+0.9219*H-0.0128*I+0.0374*J-0.0517*K+1.9069*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-18.9758</t>
+  </si>
+  <si>
+    <t>0.0780</t>
+  </si>
+  <si>
+    <t>0.0144</t>
+  </si>
+  <si>
+    <t>0.9219</t>
+  </si>
+  <si>
+    <t>0.0374</t>
+  </si>
+  <si>
+    <t>-0.0517</t>
+  </si>
+  <si>
+    <t>1.9069</t>
+  </si>
+  <si>
+    <t>-27.9736-0.0006*B+0.0000*C+0.0709*D+0.0054*E-0.0018*F+0.0000*G+0.2794*H-0.0147*I+0.0312*J-0.0780*K+0.9464*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-27.9736</t>
+  </si>
+  <si>
+    <t>0.0709</t>
+  </si>
+  <si>
+    <t>0.0054</t>
+  </si>
+  <si>
+    <t>-0.0018</t>
+  </si>
+  <si>
+    <t>0.2794</t>
+  </si>
+  <si>
+    <t>-0.0147</t>
+  </si>
+  <si>
+    <t>0.0312</t>
+  </si>
+  <si>
+    <t>-0.0780</t>
+  </si>
+  <si>
+    <t>0.9464</t>
+  </si>
+  <si>
+    <t>-53.7166-0.0003*B+0.0000*C+0.0554*D+0.0183*E-0.0030*F+0.0000*G+0.8951*H-0.0083*I+0.0266*J-0.0693*K+1.1396*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-53.7166</t>
+  </si>
+  <si>
+    <t>0.0183</t>
+  </si>
+  <si>
+    <t>-0.0030</t>
+  </si>
+  <si>
+    <t>0.8951</t>
+  </si>
+  <si>
+    <t>-0.0083</t>
+  </si>
+  <si>
+    <t>0.0266</t>
+  </si>
+  <si>
+    <t>-0.0693</t>
+  </si>
+  <si>
+    <t>1.1396</t>
+  </si>
+  <si>
+    <t>-16.4985-0.0005*B+0.0000*C+0.1012*D+0.0232*E-0.0027*F+0.0000*G+0.7895*H-0.0117*I+0.0354*J-0.0795*K+1.0989*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-16.4985</t>
+  </si>
+  <si>
+    <t>0.1012</t>
+  </si>
+  <si>
+    <t>0.0232</t>
+  </si>
+  <si>
+    <t>-0.0027</t>
+  </si>
+  <si>
+    <t>0.7895</t>
+  </si>
+  <si>
+    <t>-0.0117</t>
+  </si>
+  <si>
+    <t>0.0354</t>
+  </si>
+  <si>
+    <t>-0.0795</t>
+  </si>
+  <si>
+    <t>1.0989</t>
+  </si>
+  <si>
+    <t>-51.3957-0.0003*B+0.0000*C+0.0908*D+0.0132*E-0.0027*F+0.0000*G+1.0109*H-0.0083*I+0.0252*J-0.0754*K+0.4446*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-51.3957</t>
+  </si>
+  <si>
+    <t>0.0908</t>
+  </si>
+  <si>
+    <t>0.0132</t>
+  </si>
+  <si>
+    <t>1.0109</t>
+  </si>
+  <si>
+    <t>0.0252</t>
+  </si>
+  <si>
+    <t>-0.0754</t>
+  </si>
+  <si>
+    <t>0.4446</t>
+  </si>
+  <si>
+    <t>-1.8649+-0.0000*B+0.0000*C+0.1161*D+0.0087*E-0.0023*F+0.0000*G+0.9080*H-0.0089*I+0.0106*J-0.0826*K+0.9628*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-1.8649</t>
+  </si>
+  <si>
+    <t>-0.0000</t>
+  </si>
+  <si>
+    <t>0.1161</t>
+  </si>
+  <si>
+    <t>0.0087</t>
+  </si>
+  <si>
+    <t>0.9080</t>
+  </si>
+  <si>
+    <t>-0.0089</t>
+  </si>
+  <si>
+    <t>0.0106</t>
+  </si>
+  <si>
+    <t>-0.0826</t>
+  </si>
+  <si>
+    <t>0.9628</t>
+  </si>
+  <si>
+    <t>-24.9597-0.0006*B+0.0000*C+0.0570*D+0.0018*E-0.0019*F+0.0000*G+0.5372*H-0.0086*I+0.0065*J-0.1028*K+1.7301*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-24.9597</t>
+  </si>
+  <si>
+    <t>0.0570</t>
+  </si>
+  <si>
+    <t>0.0018</t>
+  </si>
+  <si>
+    <t>0.5372</t>
+  </si>
+  <si>
+    <t>-0.0086</t>
+  </si>
+  <si>
+    <t>0.0065</t>
+  </si>
+  <si>
+    <t>-0.1028</t>
+  </si>
+  <si>
+    <t>1.7301</t>
+  </si>
+  <si>
+    <t>-11.9519-0.0006*B+0.0000*C+0.0767*D+0.0089*E-0.0023*F+0.0000*G+0.7021*H-0.0146*I+0.0322*J-0.0700*K+1.1938*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-11.9519</t>
+  </si>
+  <si>
+    <t>0.0767</t>
+  </si>
+  <si>
+    <t>0.0089</t>
+  </si>
+  <si>
+    <t>0.7021</t>
+  </si>
+  <si>
+    <t>-0.0146</t>
+  </si>
+  <si>
+    <t>0.0322</t>
+  </si>
+  <si>
+    <t>-0.0700</t>
+  </si>
+  <si>
+    <t>1.1938</t>
+  </si>
+  <si>
+    <t>-29.9130-0.0006*B+0.0000*C+0.0941*D+0.0055*E-0.0023*F+0.0000*G+0.8879*H-0.0136*I+0.0224*J-0.0682*K+1.5597*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-29.9130</t>
+  </si>
+  <si>
+    <t>0.0941</t>
+  </si>
+  <si>
+    <t>0.0055</t>
+  </si>
+  <si>
+    <t>0.8879</t>
+  </si>
+  <si>
+    <t>-0.0136</t>
+  </si>
+  <si>
+    <t>0.0224</t>
+  </si>
+  <si>
+    <t>-0.0682</t>
+  </si>
+  <si>
+    <t>1.5597</t>
+  </si>
+  <si>
+    <t>-31.1492-0.0002*B+0.0000*C+0.0835*D+0.0077*E-0.0017*F+0.0000*G+0.8099*H-0.0051*I+0.0298*J-0.0645*K+0.9996*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-31.1492</t>
+  </si>
+  <si>
+    <t>0.0835</t>
+  </si>
+  <si>
+    <t>0.0077</t>
+  </si>
+  <si>
+    <t>0.8099</t>
+  </si>
+  <si>
+    <t>0.0298</t>
+  </si>
+  <si>
+    <t>-0.0645</t>
+  </si>
+  <si>
+    <t>0.9996</t>
+  </si>
+  <si>
+    <t>-31.8631-0.0002*B+0.0000*C+0.0554*D+0.0042*E-0.0019*F+0.0000*G+0.4003*H-0.0051*I+0.0157*J-0.0554*K+1.3340*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-31.8631</t>
+  </si>
+  <si>
+    <t>0.0042</t>
+  </si>
+  <si>
+    <t>0.4003</t>
+  </si>
+  <si>
+    <t>0.0157</t>
+  </si>
+  <si>
+    <t>-0.0554</t>
+  </si>
+  <si>
+    <t>1.3340</t>
+  </si>
+  <si>
+    <t>-22.9378-0.0002*B+0.0000*C+0.0607*D+0.0237*E-0.0019*F+0.0000*G+0.7130*H-0.0135*I+0.0269*J-0.0602*K+0.2017*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-22.9378</t>
+  </si>
+  <si>
+    <t>0.0607</t>
+  </si>
+  <si>
+    <t>0.0237</t>
+  </si>
+  <si>
+    <t>0.7130</t>
+  </si>
+  <si>
+    <t>-0.0135</t>
+  </si>
+  <si>
+    <t>0.0269</t>
+  </si>
+  <si>
+    <t>-0.0602</t>
+  </si>
+  <si>
+    <t>0.2017</t>
+  </si>
+  <si>
+    <t>-35.6802-0.0004*B+0.0000*C+0.0660*D+0.0087*E-0.0025*F+0.0000*G+0.8499*H-0.0136*I+0.0249*J-0.0846*K+1.3272*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-35.6802</t>
+  </si>
+  <si>
+    <t>0.0660</t>
+  </si>
+  <si>
+    <t>0.8499</t>
+  </si>
+  <si>
+    <t>0.0249</t>
+  </si>
+  <si>
+    <t>-0.0846</t>
+  </si>
+  <si>
+    <t>1.3272</t>
+  </si>
+  <si>
+    <t>-64.4614-0.0002*B+0.0000*C+0.0678*D+0.0134*E-0.0016*F+0.0000*G+0.8549*H-0.0085*I+0.0151*J-0.0673*K+0.4132*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-64.4614</t>
+  </si>
+  <si>
+    <t>0.0678</t>
+  </si>
+  <si>
+    <t>0.0134</t>
+  </si>
+  <si>
+    <t>-0.0016</t>
+  </si>
+  <si>
+    <t>0.8549</t>
+  </si>
+  <si>
+    <t>-0.0085</t>
+  </si>
+  <si>
+    <t>0.0151</t>
+  </si>
+  <si>
+    <t>-0.0673</t>
+  </si>
+  <si>
+    <t>0.4132</t>
+  </si>
+  <si>
+    <t>-25.1518-0.0006*B+0.0000*C+0.0888*D+0.0184*E-0.0023*F+0.0000*G+1.1406*H-0.0079*I+0.0169*J-0.0525*K+1.8935*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-25.1518</t>
+  </si>
+  <si>
+    <t>0.0888</t>
+  </si>
+  <si>
+    <t>0.0184</t>
+  </si>
+  <si>
+    <t>1.1406</t>
+  </si>
+  <si>
+    <t>-0.0525</t>
+  </si>
+  <si>
+    <t>1.8935</t>
+  </si>
+  <si>
+    <t>-22.8658-0.0007*B+0.0000*C+0.0835*D+0.0196*E-0.0021*F+0.0000*G+0.8481*H-0.0062*I+0.0259*J-0.0808*K+0.7461*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-22.8658</t>
+  </si>
+  <si>
+    <t>-0.0007</t>
+  </si>
+  <si>
+    <t>0.0196</t>
+  </si>
+  <si>
+    <t>0.8481</t>
+  </si>
+  <si>
+    <t>-0.0062</t>
+  </si>
+  <si>
+    <t>0.0259</t>
+  </si>
+  <si>
+    <t>-0.0808</t>
+  </si>
+  <si>
+    <t>0.7461</t>
+  </si>
+  <si>
+    <t>-38.0154-0.0002*B+0.0000*C+0.0905*D+0.0186*E-0.0023*F+0.0000*G+0.4544*H-0.0108*I+0.0065*J-0.0716*K+1.6288*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-38.0154</t>
+  </si>
+  <si>
+    <t>0.0186</t>
+  </si>
+  <si>
+    <t>0.4544</t>
+  </si>
+  <si>
+    <t>-0.0108</t>
+  </si>
+  <si>
+    <t>-0.0716</t>
+  </si>
+  <si>
+    <t>1.6288</t>
+  </si>
+  <si>
+    <t>-36.8535-0.0003*B+0.0000*C+0.0696*D+0.0164*E-0.0019*F+0.0000*G+0.8912*H-0.0115*I+0.0209*J-0.0715*K+1.0361*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-36.8535</t>
+  </si>
+  <si>
+    <t>0.0696</t>
+  </si>
+  <si>
+    <t>0.0164</t>
+  </si>
+  <si>
+    <t>0.8912</t>
+  </si>
+  <si>
+    <t>-0.0115</t>
+  </si>
+  <si>
+    <t>0.0209</t>
+  </si>
+  <si>
+    <t>-0.0715</t>
+  </si>
+  <si>
+    <t>1.0361</t>
+  </si>
+  <si>
+    <t>-29.7817-0.0004*B+0.0000*C+0.1034*D+0.0020*E-0.0025*F+0.0000*G+1.1804*H-0.0063*I+0.0212*J-0.0835*K+1.6022*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-29.7817</t>
+  </si>
+  <si>
+    <t>0.1034</t>
+  </si>
+  <si>
+    <t>0.0020</t>
+  </si>
+  <si>
+    <t>1.1804</t>
+  </si>
+  <si>
+    <t>-0.0063</t>
+  </si>
+  <si>
+    <t>0.0212</t>
+  </si>
+  <si>
+    <t>-0.0835</t>
+  </si>
+  <si>
+    <t>1.6022</t>
+  </si>
+  <si>
+    <t>-18.5957-0.0002*B+0.0000*C+0.0554*D+0.0131*E-0.0026*F+0.0000*G+0.7512*H-0.0148*I+0.0324*J-0.0688*K+0.6504*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-18.5957</t>
+  </si>
+  <si>
+    <t>0.0131</t>
+  </si>
+  <si>
+    <t>-0.0026</t>
+  </si>
+  <si>
+    <t>0.7512</t>
+  </si>
+  <si>
+    <t>-0.0148</t>
+  </si>
+  <si>
+    <t>0.0324</t>
+  </si>
+  <si>
+    <t>-0.0688</t>
+  </si>
+  <si>
+    <t>0.6504</t>
+  </si>
+  <si>
+    <t>-33.6670-0.0010*B+0.0000*C+0.0683*D+0.0217*E-0.0023*F+0.0000*G+0.9621*H-0.0061*I+0.0298*J-0.0913*K+1.0198*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-33.6670</t>
+  </si>
+  <si>
+    <t>-0.0010</t>
+  </si>
+  <si>
+    <t>0.0683</t>
+  </si>
+  <si>
+    <t>0.0217</t>
+  </si>
+  <si>
+    <t>0.9621</t>
+  </si>
+  <si>
+    <t>-0.0061</t>
+  </si>
+  <si>
+    <t>-0.0913</t>
+  </si>
+  <si>
+    <t>1.0198</t>
+  </si>
+  <si>
+    <t>-6.5920+0.0000*B+0.0000*C+0.1107*D+0.0194*E-0.0023*F+0.0000*G+0.9094*H-0.0088*I+0.0149*J-0.1012*K+1.2176*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-6.5920</t>
+  </si>
+  <si>
+    <t>0.1107</t>
+  </si>
+  <si>
+    <t>0.0194</t>
+  </si>
+  <si>
+    <t>0.9094</t>
+  </si>
+  <si>
+    <t>-0.0088</t>
+  </si>
+  <si>
+    <t>0.0149</t>
+  </si>
+  <si>
+    <t>-0.1012</t>
+  </si>
+  <si>
+    <t>1.2176</t>
+  </si>
+  <si>
+    <t>-64.3150-0.0007*B+0.0000*C+0.0781*D+0.0046*E-0.0021*F+0.0000*G+0.3531*H-0.0162*I+0.0151*J-0.0982*K+1.5761*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-64.3150</t>
+  </si>
+  <si>
+    <t>0.0781</t>
+  </si>
+  <si>
+    <t>0.0046</t>
+  </si>
+  <si>
+    <t>0.3531</t>
+  </si>
+  <si>
+    <t>-0.0162</t>
+  </si>
+  <si>
+    <t>-0.0982</t>
+  </si>
+  <si>
+    <t>1.5761</t>
+  </si>
+  <si>
+    <t>-47.2556-0.0002*B+0.0000*C+0.0554*D+0.0180*E-0.0018*F+0.0000*G+0.9138*H-0.0178*I+0.0195*J-0.0822*K+0.6207*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-47.2556</t>
+  </si>
+  <si>
+    <t>0.0180</t>
+  </si>
+  <si>
+    <t>0.9138</t>
+  </si>
+  <si>
+    <t>-0.0178</t>
+  </si>
+  <si>
+    <t>0.0195</t>
+  </si>
+  <si>
+    <t>-0.0822</t>
+  </si>
+  <si>
+    <t>0.6207</t>
+  </si>
+  <si>
+    <t>-10.4572-0.0003*B+0.0000*C+0.0875*D+0.0125*E-0.0020*F+0.0000*G+0.3910*H-0.0066*I+0.0123*J-0.1101*K+0.6805*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-10.4572</t>
+  </si>
+  <si>
+    <t>0.0875</t>
+  </si>
+  <si>
+    <t>0.0125</t>
+  </si>
+  <si>
+    <t>0.3910</t>
+  </si>
+  <si>
+    <t>-0.0066</t>
+  </si>
+  <si>
+    <t>0.0123</t>
+  </si>
+  <si>
+    <t>-0.1101</t>
+  </si>
+  <si>
+    <t>0.6805</t>
+  </si>
+  <si>
+    <t>-43.3260-0.0008*B+0.0000*C+0.0639*D+0.0112*E-0.0027*F+0.0000*G+1.3807*H-0.0068*I+0.0270*J-0.1178*K+1.3806*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-43.3260</t>
+  </si>
+  <si>
+    <t>-0.0008</t>
+  </si>
+  <si>
+    <t>0.0639</t>
+  </si>
+  <si>
+    <t>0.0112</t>
+  </si>
+  <si>
+    <t>1.3807</t>
+  </si>
+  <si>
+    <t>-0.0068</t>
+  </si>
+  <si>
+    <t>0.0270</t>
+  </si>
+  <si>
+    <t>-0.1178</t>
+  </si>
+  <si>
+    <t>1.3806</t>
+  </si>
+  <si>
+    <t>-1.8649-0.0002*B+0.0000*C+0.1175*D+0.0162*E-0.0022*F+0.0000*G+0.7350*H-0.0103*I+0.0248*J-0.1195*K+0.2967*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>0.1175</t>
+  </si>
+  <si>
+    <t>0.0162</t>
+  </si>
+  <si>
+    <t>-0.0022</t>
+  </si>
+  <si>
+    <t>0.7350</t>
+  </si>
+  <si>
+    <t>-0.0103</t>
+  </si>
+  <si>
+    <t>0.0248</t>
+  </si>
+  <si>
+    <t>-0.1195</t>
+  </si>
+  <si>
+    <t>0.2967</t>
+  </si>
+  <si>
+    <t>-26.5105-0.0003*B+0.0000*C+0.1140*D+0.0084*E-0.0029*F+0.0000*G+1.0745*H-0.0090*I+0.0266*J-0.0903*K+0.4055*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-26.5105</t>
+  </si>
+  <si>
+    <t>0.1140</t>
+  </si>
+  <si>
+    <t>0.0084</t>
+  </si>
+  <si>
+    <t>-0.0029</t>
+  </si>
+  <si>
+    <t>1.0745</t>
+  </si>
+  <si>
+    <t>-0.0090</t>
+  </si>
+  <si>
+    <t>-0.0903</t>
+  </si>
+  <si>
+    <t>0.4055</t>
+  </si>
+  <si>
+    <t>-32.1222-0.0004*B+0.0000*C+0.0760*D+0.0103*E-0.0028*F+0.0000*G+0.7534*H-0.0101*I+0.0226*J-0.0771*K+1.3145*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-32.1222</t>
+  </si>
+  <si>
+    <t>0.0760</t>
+  </si>
+  <si>
+    <t>0.0103</t>
+  </si>
+  <si>
+    <t>-0.0028</t>
+  </si>
+  <si>
+    <t>0.7534</t>
+  </si>
+  <si>
+    <t>-0.0101</t>
+  </si>
+  <si>
+    <t>0.0226</t>
+  </si>
+  <si>
+    <t>-0.0771</t>
+  </si>
+  <si>
+    <t>1.3145</t>
+  </si>
+  <si>
+    <t>-26.3898-0.0004*B+0.0000*C+0.0822*D+0.0129*E-0.0018*F+0.0000*G+0.4973*H-0.0115*I+0.0069*J-0.0524*K+1.6041*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-26.3898</t>
+  </si>
+  <si>
+    <t>0.0822</t>
+  </si>
+  <si>
+    <t>0.0129</t>
+  </si>
+  <si>
+    <t>0.4973</t>
+  </si>
+  <si>
+    <t>0.0069</t>
+  </si>
+  <si>
+    <t>-0.0524</t>
+  </si>
+  <si>
+    <t>1.6041</t>
+  </si>
+  <si>
+    <t>-44.8432-0.0003*B+0.0000*C+0.1081*D+0.0071*E-0.0024*F+0.0000*G+0.8112*H-0.0051*I+0.0272*J-0.0521*K+0.4015*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-44.8432</t>
+  </si>
+  <si>
+    <t>0.1081</t>
+  </si>
+  <si>
+    <t>-0.0024</t>
+  </si>
+  <si>
+    <t>0.8112</t>
+  </si>
+  <si>
+    <t>0.0272</t>
+  </si>
+  <si>
+    <t>-0.0521</t>
+  </si>
+  <si>
+    <t>0.4015</t>
+  </si>
+  <si>
+    <t>-6.4865-0.0005*B+0.0000*C+0.0707*D+0.0133*E-0.0023*F+0.0000*G+0.8234*H-0.0095*I+0.0216*J-0.0541*K+0.8125*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-6.4865</t>
+  </si>
+  <si>
+    <t>0.0707</t>
+  </si>
+  <si>
+    <t>0.0133</t>
+  </si>
+  <si>
+    <t>0.8234</t>
+  </si>
+  <si>
+    <t>-0.0095</t>
+  </si>
+  <si>
+    <t>0.0216</t>
+  </si>
+  <si>
+    <t>-0.0541</t>
+  </si>
+  <si>
+    <t>0.8125</t>
+  </si>
+  <si>
+    <t>-58.6335-0.0001*B+0.0000*C+0.0877*D+0.0079*E-0.0021*F+0.0000*G+0.6104*H-0.0051*I+0.0082*J-0.0468*K+1.1768*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-58.6335</t>
+  </si>
+  <si>
+    <t>-0.0001</t>
+  </si>
+  <si>
+    <t>0.0877</t>
+  </si>
+  <si>
+    <t>0.0079</t>
+  </si>
+  <si>
+    <t>0.6104</t>
+  </si>
+  <si>
+    <t>0.0082</t>
+  </si>
+  <si>
+    <t>-0.0468</t>
+  </si>
+  <si>
+    <t>1.1768</t>
+  </si>
+  <si>
+    <t>-44.7821-0.0007*B+0.0000*C+0.0925*D+0.0006*E-0.0026*F+0.0000*G+0.4347*H-0.0092*I+0.0209*J-0.0454*K+1.5031*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-44.7821</t>
+  </si>
+  <si>
+    <t>0.0925</t>
+  </si>
+  <si>
+    <t>0.0006</t>
+  </si>
+  <si>
+    <t>0.4347</t>
+  </si>
+  <si>
+    <t>-0.0454</t>
+  </si>
+  <si>
+    <t>1.5031</t>
+  </si>
+  <si>
+    <t>-50.8374-0.0004*B+0.0000*C+0.0971*D+0.0126*E-0.0021*F+0.0000*G+0.9377*H-0.0078*I+0.0121*J-0.0768*K+1.3865*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-50.8374</t>
+  </si>
+  <si>
+    <t>0.0971</t>
+  </si>
+  <si>
+    <t>0.9377</t>
+  </si>
+  <si>
+    <t>-0.0078</t>
+  </si>
+  <si>
+    <t>0.0121</t>
+  </si>
+  <si>
+    <t>-0.0768</t>
+  </si>
+  <si>
+    <t>1.3865</t>
+  </si>
+  <si>
+    <t>-3.5721-0.0007*B+0.0000*C+0.0763*D+0.0093*E-0.0023*F+0.0000*G+0.6314*H-0.0160*I+0.0107*J-0.0454*K+0.8540*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-3.5721</t>
+  </si>
+  <si>
+    <t>0.0763</t>
+  </si>
+  <si>
+    <t>0.0093</t>
+  </si>
+  <si>
+    <t>0.6314</t>
+  </si>
+  <si>
+    <t>-0.0160</t>
+  </si>
+  <si>
+    <t>0.0107</t>
+  </si>
+  <si>
+    <t>0.8540</t>
+  </si>
+  <si>
+    <t>-3.1653-0.0001*B+0.0000*C+0.0727*D+0.0134*E-0.0018*F+0.0000*G+0.5543*H-0.0134*I+0.0105*J-0.0884*K+1.0649*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-3.1653</t>
+  </si>
+  <si>
+    <t>0.0727</t>
+  </si>
+  <si>
+    <t>0.5543</t>
+  </si>
+  <si>
+    <t>-0.0134</t>
+  </si>
+  <si>
+    <t>-0.0884</t>
+  </si>
+  <si>
+    <t>1.0649</t>
+  </si>
+  <si>
+    <t>-34.1402-0.0006*B+0.0000*C+0.0810*D+0.0113*E-0.0024*F+0.0000*G+0.7321*H-0.0170*I+0.0246*J-0.0632*K+1.3276*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-34.1402</t>
+  </si>
+  <si>
+    <t>0.0810</t>
+  </si>
+  <si>
+    <t>0.7321</t>
+  </si>
+  <si>
+    <t>-0.0170</t>
+  </si>
+  <si>
+    <t>0.0246</t>
+  </si>
+  <si>
+    <t>-0.0632</t>
+  </si>
+  <si>
+    <t>1.3276</t>
+  </si>
+  <si>
+    <t>-39.3277-0.0004*B+0.0000*C+0.1098*D+0.0114*E-0.0021*F+0.0000*G+0.8121*H-0.0170*I+0.0159*J-0.0688*K+1.5752*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-39.3277</t>
+  </si>
+  <si>
+    <t>0.1098</t>
+  </si>
+  <si>
+    <t>0.0114</t>
+  </si>
+  <si>
+    <t>0.8121</t>
+  </si>
+  <si>
+    <t>0.0159</t>
+  </si>
+  <si>
+    <t>1.5752</t>
+  </si>
+  <si>
+    <t>-18.9748-0.0007*B+0.0000*C+0.0554*D+0.0066*E-0.0024*F+0.0000*G+0.3200*H-0.0081*I+0.0470*J-0.0777*K+0.8507*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-18.9748</t>
+  </si>
+  <si>
+    <t>0.0066</t>
+  </si>
+  <si>
+    <t>0.3200</t>
+  </si>
+  <si>
+    <t>-0.0081</t>
+  </si>
+  <si>
+    <t>0.0470</t>
+  </si>
+  <si>
+    <t>-0.0777</t>
+  </si>
+  <si>
+    <t>0.8507</t>
+  </si>
+  <si>
+    <t>-35.7990-0.0007*B+0.0000*C+0.0725*D+0.0167*E-0.0026*F+0.0000*G+0.2794*H-0.0066*I+0.0251*J-0.0972*K+1.2813*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-35.7990</t>
+  </si>
+  <si>
+    <t>0.0725</t>
+  </si>
+  <si>
+    <t>0.0167</t>
+  </si>
+  <si>
+    <t>-0.0972</t>
+  </si>
+  <si>
+    <t>1.2813</t>
+  </si>
+  <si>
+    <t>-20.4611-0.0003*B+0.0000*C+0.0704*D+0.0149*E-0.0016*F+0.0000*G+0.7549*H-0.0092*I+0.0266*J-0.0753*K+0.9868*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-20.4611</t>
+  </si>
+  <si>
+    <t>0.0704</t>
+  </si>
+  <si>
+    <t>0.7549</t>
+  </si>
+  <si>
+    <t>-0.0753</t>
+  </si>
+  <si>
+    <t>0.9868</t>
+  </si>
+  <si>
+    <t>-27.3053-0.0007*B+0.0000*C+0.0629*D+0.0092*E-0.0016*F+0.0000*G+0.7294*H-0.0090*I+0.0282*J-0.0961*K+0.2017*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-27.3053</t>
+  </si>
+  <si>
+    <t>0.0629</t>
+  </si>
+  <si>
+    <t>0.0092</t>
+  </si>
+  <si>
+    <t>0.7294</t>
+  </si>
+  <si>
+    <t>0.0282</t>
+  </si>
+  <si>
+    <t>-0.0961</t>
+  </si>
+  <si>
+    <t>-20.6408-0.0001*B+0.0000*C+0.0808*D+0.0079*E-0.0025*F+0.0000*G+0.5706*H-0.0070*I+0.0212*J-0.0723*K+0.6611*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-20.6408</t>
+  </si>
+  <si>
+    <t>0.0808</t>
+  </si>
+  <si>
+    <t>0.5706</t>
+  </si>
+  <si>
+    <t>-0.0070</t>
+  </si>
+  <si>
+    <t>-0.0723</t>
+  </si>
+  <si>
+    <t>0.6611</t>
+  </si>
+  <si>
+    <t>-32.8709-0.0006*B+0.0000*C+0.0639*D+0.0144*E-0.0016*F+0.0000*G+0.5335*H-0.0107*I+0.0314*J-0.1046*K+1.3621*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-32.8709</t>
+  </si>
+  <si>
+    <t>0.5335</t>
+  </si>
+  <si>
+    <t>-0.0107</t>
+  </si>
+  <si>
+    <t>0.0314</t>
+  </si>
+  <si>
+    <t>-0.1046</t>
+  </si>
+  <si>
+    <t>1.3621</t>
+  </si>
+  <si>
+    <t>-42.1097-0.0007*B+0.0000*C+0.0855*D+0.0162*E-0.0022*F+0.0000*G+0.9370*H-0.0092*I+0.0226*J-0.0512*K+1.5357*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-42.1097</t>
+  </si>
+  <si>
+    <t>0.0855</t>
+  </si>
+  <si>
+    <t>0.9370</t>
+  </si>
+  <si>
+    <t>-0.0512</t>
+  </si>
+  <si>
+    <t>1.5357</t>
+  </si>
+  <si>
+    <t>-21.3999-0.0003*B+0.0000*C+0.0554*D+0.0136*E-0.0025*F+0.0000*G+0.4503*H-0.0108*I+0.0143*J-0.0624*K+0.6722*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-21.3999</t>
+  </si>
+  <si>
+    <t>0.0136</t>
+  </si>
+  <si>
+    <t>0.4503</t>
+  </si>
+  <si>
+    <t>0.0143</t>
+  </si>
+  <si>
+    <t>-0.0624</t>
+  </si>
+  <si>
+    <t>0.6722</t>
+  </si>
+  <si>
+    <t>-32.1463-0.0005*B+0.0000*C+0.0770*D-0.0001*E-0.0021*F+0.0000*G+0.2794*H-0.0146*I+0.0143*J-0.0620*K+1.6357*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-32.1463</t>
+  </si>
+  <si>
+    <t>0.0770</t>
+  </si>
+  <si>
+    <t>-0.0620</t>
+  </si>
+  <si>
+    <t>1.6357</t>
+  </si>
+  <si>
+    <t>-11.3614-0.0005*B+0.0000*C+0.0571*D+0.0140*E-0.0024*F+0.0000*G+0.6584*H-0.0096*I+0.0459*J-0.0727*K+1.3550*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-11.3614</t>
+  </si>
+  <si>
+    <t>0.0571</t>
+  </si>
+  <si>
+    <t>0.0140</t>
+  </si>
+  <si>
+    <t>0.6584</t>
+  </si>
+  <si>
+    <t>-0.0096</t>
+  </si>
+  <si>
+    <t>0.0459</t>
+  </si>
+  <si>
+    <t>-0.0727</t>
+  </si>
+  <si>
+    <t>1.3550</t>
+  </si>
+  <si>
+    <t>-16.8139-0.0003*B+0.0000*C+0.0882*D+0.0131*E-0.0019*F+0.0000*G+0.7366*H-0.0073*I+0.0168*J-0.0674*K+1.1184*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-16.8139</t>
+  </si>
+  <si>
+    <t>0.0882</t>
+  </si>
+  <si>
+    <t>0.7366</t>
+  </si>
+  <si>
+    <t>-0.0073</t>
+  </si>
+  <si>
+    <t>0.0168</t>
+  </si>
+  <si>
+    <t>-0.0674</t>
+  </si>
+  <si>
+    <t>1.1184</t>
+  </si>
+  <si>
+    <t>-15.9381-0.0002*B+0.0000*C+0.0565*D+0.0148*E-0.0024*F+0.0000*G+0.8884*H-0.0051*I+0.0281*J-0.0567*K+0.9746*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-15.9381</t>
+  </si>
+  <si>
+    <t>0.0565</t>
+  </si>
+  <si>
+    <t>0.0148</t>
+  </si>
+  <si>
+    <t>0.8884</t>
+  </si>
+  <si>
+    <t>0.0281</t>
+  </si>
+  <si>
+    <t>-0.0567</t>
+  </si>
+  <si>
+    <t>0.9746</t>
+  </si>
+  <si>
+    <t>-25.7697-0.0004*B+0.0000*C+0.0717*D+0.0104*E-0.0032*F+0.0000*G+0.7990*H-0.0112*I+0.0265*J-0.0454*K+0.5385*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-25.7697</t>
+  </si>
+  <si>
+    <t>0.0717</t>
+  </si>
+  <si>
+    <t>0.0104</t>
+  </si>
+  <si>
+    <t>-0.0032</t>
+  </si>
+  <si>
+    <t>0.7990</t>
+  </si>
+  <si>
+    <t>0.0265</t>
+  </si>
+  <si>
+    <t>0.5385</t>
+  </si>
+  <si>
+    <t>-20.8363-0.0006*B+0.0000*C+0.1083*D+0.0152*E-0.0024*F+0.0000*G+0.2794*H-0.0134*I+0.0148*J-0.1159*K+0.8402*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-20.8363</t>
+  </si>
+  <si>
+    <t>0.1083</t>
+  </si>
+  <si>
+    <t>0.0152</t>
+  </si>
+  <si>
+    <t>-0.1159</t>
+  </si>
+  <si>
+    <t>0.8402</t>
+  </si>
+  <si>
+    <t>-51.4295-0.0006*B+0.0000*C+0.0942*D+0.0103*E-0.0018*F+0.0000*G+0.6839*H-0.0132*I+0.0330*J-0.0597*K+0.9780*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-51.4295</t>
+  </si>
+  <si>
+    <t>0.0942</t>
+  </si>
+  <si>
+    <t>0.6839</t>
+  </si>
+  <si>
+    <t>-0.0132</t>
+  </si>
+  <si>
+    <t>0.0330</t>
+  </si>
+  <si>
+    <t>-0.0597</t>
+  </si>
+  <si>
+    <t>0.9780</t>
+  </si>
+  <si>
+    <t>-16.5699-0.0004*B+0.0000*C+0.0742*D+0.0104*E-0.0022*F+0.0000*G+0.7187*H-0.0113*I+0.0367*J-0.0692*K+1.2487*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-16.5699</t>
+  </si>
+  <si>
+    <t>0.0742</t>
+  </si>
+  <si>
+    <t>0.7187</t>
+  </si>
+  <si>
+    <t>-0.0113</t>
+  </si>
+  <si>
+    <t>0.0367</t>
+  </si>
+  <si>
+    <t>-0.0692</t>
+  </si>
+  <si>
+    <t>1.2487</t>
+  </si>
+  <si>
+    <t>-34.9934-0.0007*B+0.0000*C+0.0745*D+0.0063*E-0.0019*F+0.0000*G+0.7615*H-0.0129*I+0.0324*J-0.0454*K+0.4882*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-34.9934</t>
+  </si>
+  <si>
+    <t>0.0745</t>
+  </si>
+  <si>
+    <t>0.0063</t>
+  </si>
+  <si>
+    <t>0.7615</t>
+  </si>
+  <si>
+    <t>-0.0129</t>
+  </si>
+  <si>
+    <t>0.4882</t>
+  </si>
+  <si>
+    <t>-19.0840-0.0001*B+0.0000*C+0.0554*D+0.0175*E-0.0024*F+0.0000*G+1.0629*H-0.0095*I+0.0420*J-0.0618*K+0.5812*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-19.0840</t>
+  </si>
+  <si>
+    <t>0.0175</t>
+  </si>
+  <si>
+    <t>1.0629</t>
+  </si>
+  <si>
+    <t>0.0420</t>
+  </si>
+  <si>
+    <t>-0.0618</t>
+  </si>
+  <si>
+    <t>0.5812</t>
+  </si>
+  <si>
+    <t>-29.3207-0.0004*B+0.0000*C+0.0924*D+0.0146*E-0.0025*F+0.0000*G+0.9066*H-0.0109*I+0.0108*J-0.1170*K+0.2017*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-29.3207</t>
+  </si>
+  <si>
+    <t>0.0924</t>
+  </si>
+  <si>
+    <t>0.0146</t>
+  </si>
+  <si>
+    <t>0.9066</t>
+  </si>
+  <si>
+    <t>-0.0109</t>
+  </si>
+  <si>
+    <t>0.0108</t>
+  </si>
+  <si>
+    <t>-0.1170</t>
+  </si>
+  <si>
+    <t>-16.7412-0.0003*B+0.0000*C+0.0762*D+0.0034*E-0.0018*F+0.0000*G+0.5526*H-0.0073*I+0.0268*J-0.0852*K+1.1417*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-16.7412</t>
+  </si>
+  <si>
+    <t>0.0762</t>
+  </si>
+  <si>
+    <t>0.0034</t>
+  </si>
+  <si>
+    <t>0.5526</t>
+  </si>
+  <si>
+    <t>0.0268</t>
+  </si>
+  <si>
+    <t>-0.0852</t>
+  </si>
+  <si>
+    <t>1.1417</t>
+  </si>
+  <si>
+    <t>-32.7649-0.0002*B+0.0000*C+0.0776*D+0.0114*E-0.0026*F+0.0000*G+0.4756*H-0.0157*I+0.0082*J-0.0963*K+0.3287*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-32.7649</t>
+  </si>
+  <si>
+    <t>0.0776</t>
+  </si>
+  <si>
+    <t>0.4756</t>
+  </si>
+  <si>
+    <t>-0.0157</t>
+  </si>
+  <si>
+    <t>-0.0963</t>
+  </si>
+  <si>
+    <t>0.3287</t>
+  </si>
+  <si>
+    <t>-14.9379+0.0000*B+0.0000*C+0.0707*D+0.0169*E-0.0020*F+0.0000*G+0.9788*H-0.0133*I+0.0247*J-0.0751*K+0.4312*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-14.9379</t>
+  </si>
+  <si>
+    <t>0.9788</t>
+  </si>
+  <si>
+    <t>-0.0133</t>
+  </si>
+  <si>
+    <t>0.0247</t>
+  </si>
+  <si>
+    <t>-0.0751</t>
+  </si>
+  <si>
+    <t>0.4312</t>
+  </si>
+  <si>
+    <t>-8.6105-0.0008*B+0.0000*C+0.0581*D+0.0151*E-0.0026*F+0.0000*G+0.4502*H-0.0142*I+0.0100*J-0.1047*K+1.7519*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-8.6105</t>
+  </si>
+  <si>
+    <t>0.0581</t>
+  </si>
+  <si>
+    <t>0.4502</t>
+  </si>
+  <si>
+    <t>-0.0142</t>
+  </si>
+  <si>
+    <t>0.0100</t>
+  </si>
+  <si>
+    <t>-0.1047</t>
+  </si>
+  <si>
+    <t>1.7519</t>
+  </si>
+  <si>
+    <t>-53.9237+0.0000*B+0.0000*C+0.0651*D+0.0169*E-0.0031*F+0.0000*G+0.7375*H-0.0171*I+0.0187*J-0.0638*K+0.5540*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-53.9237</t>
+  </si>
+  <si>
+    <t>0.0651</t>
+  </si>
+  <si>
+    <t>-0.0031</t>
+  </si>
+  <si>
+    <t>0.7375</t>
+  </si>
+  <si>
+    <t>-0.0171</t>
+  </si>
+  <si>
+    <t>0.0187</t>
+  </si>
+  <si>
+    <t>-0.0638</t>
+  </si>
+  <si>
+    <t>0.5540</t>
+  </si>
+  <si>
+    <t>-38.4560-0.0006*B+0.0000*C+0.0611*D+0.0135*E-0.0025*F+0.0000*G+0.6781*H-0.0134*I+0.0238*J-0.0886*K+1.3914*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-38.4560</t>
+  </si>
+  <si>
+    <t>0.0611</t>
+  </si>
+  <si>
+    <t>0.0135</t>
+  </si>
+  <si>
+    <t>0.6781</t>
+  </si>
+  <si>
+    <t>0.0238</t>
+  </si>
+  <si>
+    <t>-0.0886</t>
+  </si>
+  <si>
+    <t>1.3914</t>
+  </si>
+  <si>
+    <t>-25.2300-0.0003*B+0.0000*C+0.0911*D+0.0111*E-0.0023*F+0.0000*G+0.5513*H-0.0148*I+0.0119*J-0.0589*K+1.2172*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-25.2300</t>
+  </si>
+  <si>
+    <t>0.0911</t>
+  </si>
+  <si>
+    <t>0.5513</t>
+  </si>
+  <si>
+    <t>0.0119</t>
+  </si>
+  <si>
+    <t>-0.0589</t>
+  </si>
+  <si>
+    <t>1.2172</t>
+  </si>
+  <si>
+    <t>-18.2272-0.0006*B+0.0000*C+0.0915*D+0.0117*E-0.0028*F+0.0000*G+0.8980*H-0.0116*I+0.0373*J-0.0894*K+2.0978*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-18.2272</t>
+  </si>
+  <si>
+    <t>0.0915</t>
+  </si>
+  <si>
+    <t>0.0117</t>
+  </si>
+  <si>
+    <t>0.8980</t>
+  </si>
+  <si>
+    <t>-0.0116</t>
+  </si>
+  <si>
+    <t>0.0373</t>
+  </si>
+  <si>
+    <t>-0.0894</t>
+  </si>
+  <si>
+    <t>2.0978</t>
+  </si>
+  <si>
+    <t>-54.1439-0.0005*B+0.0000*C+0.0824*D+0.0128*E-0.0020*F+0.0000*G+0.5261*H-0.0126*I+0.0106*J-0.0697*K+0.6795*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-54.1439</t>
+  </si>
+  <si>
+    <t>0.0128</t>
+  </si>
+  <si>
+    <t>0.5261</t>
+  </si>
+  <si>
+    <t>-0.0126</t>
+  </si>
+  <si>
+    <t>-0.0697</t>
+  </si>
+  <si>
+    <t>0.6795</t>
+  </si>
+  <si>
+    <t>-39.4655-0.0007*B+0.0000*C+0.1057*D-0.0001*E-0.0022*F+0.0000*G+0.8964*H-0.0091*I+0.0169*J-0.0736*K+1.9683*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-39.4655</t>
+  </si>
+  <si>
+    <t>0.1057</t>
+  </si>
+  <si>
+    <t>0.8964</t>
+  </si>
+  <si>
+    <t>-0.0091</t>
+  </si>
+  <si>
+    <t>-0.0736</t>
+  </si>
+  <si>
+    <t>1.9683</t>
+  </si>
+  <si>
+    <t>-27.8189-0.0004*B+0.0000*C+0.0733*D+0.0207*E-0.0023*F+0.0000*G+0.3864*H-0.0081*I+0.0154*J-0.0618*K+0.6908*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-27.8189</t>
+  </si>
+  <si>
+    <t>0.0733</t>
+  </si>
+  <si>
+    <t>0.0207</t>
+  </si>
+  <si>
+    <t>0.3864</t>
+  </si>
+  <si>
+    <t>0.0154</t>
+  </si>
+  <si>
+    <t>0.6908</t>
+  </si>
+  <si>
+    <t>-65.6241+-0.0000*B+0.0000*C+0.0554*D+0.0146*E-0.0027*F+0.0000*G+0.3030*H-0.0082*I+0.0320*J-0.0642*K+1.4778*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-65.6241</t>
+  </si>
+  <si>
+    <t>0.3030</t>
+  </si>
+  <si>
+    <t>-0.0082</t>
+  </si>
+  <si>
+    <t>0.0320</t>
+  </si>
+  <si>
+    <t>1.4778</t>
+  </si>
+  <si>
+    <t>-44.8053-0.0001*B+0.0000*C+0.0699*D+0.0171*E-0.0018*F+0.0000*G+0.9678*H-0.0088*I+0.0252*J-0.0944*K+1.8097*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-44.8053</t>
+  </si>
+  <si>
+    <t>0.0699</t>
+  </si>
+  <si>
+    <t>0.0171</t>
+  </si>
+  <si>
+    <t>0.9678</t>
+  </si>
+  <si>
+    <t>-0.0944</t>
+  </si>
+  <si>
+    <t>1.8097</t>
+  </si>
+  <si>
+    <t>-36.2642-0.0003*B+0.0000*C+0.0603*D+0.0082*E-0.0030*F+0.0000*G+0.4004*H-0.0051*I+0.0352*J-0.0944*K+1.1212*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-36.2642</t>
+  </si>
+  <si>
+    <t>0.0603</t>
+  </si>
+  <si>
+    <t>0.4004</t>
+  </si>
+  <si>
+    <t>0.0352</t>
+  </si>
+  <si>
+    <t>1.1212</t>
+  </si>
+  <si>
+    <t>-27.3577-0.0002*B+0.0000*C+0.0658*D+0.0132*E-0.0026*F+0.0000*G+0.9111*H-0.0148*I+0.0142*J-0.0740*K+1.1796*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-27.3577</t>
+  </si>
+  <si>
+    <t>0.0658</t>
+  </si>
+  <si>
+    <t>0.9111</t>
+  </si>
+  <si>
+    <t>0.0142</t>
+  </si>
+  <si>
+    <t>-0.0740</t>
+  </si>
+  <si>
+    <t>1.1796</t>
+  </si>
+  <si>
+    <t>-25.2425-0.0006*B+0.0000*C+0.0612*D+0.0061*E-0.0027*F+0.0000*G+0.6339*H-0.0051*I+0.0237*J-0.0812*K+0.7498*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-25.2425</t>
+  </si>
+  <si>
+    <t>0.0612</t>
+  </si>
+  <si>
+    <t>0.0061</t>
+  </si>
+  <si>
+    <t>0.6339</t>
+  </si>
+  <si>
+    <t>-0.0812</t>
+  </si>
+  <si>
+    <t>0.7498</t>
+  </si>
+  <si>
+    <t>-63.6950+0.0000*B+0.0000*C+0.0760*D+0.0082*E-0.0026*F+0.0000*G+0.2794*H-0.0094*I+0.0392*J-0.0616*K+2.2521*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-63.6950</t>
+  </si>
+  <si>
+    <t>-0.0094</t>
+  </si>
+  <si>
+    <t>0.0392</t>
+  </si>
+  <si>
+    <t>-0.0616</t>
+  </si>
+  <si>
+    <t>2.2521</t>
+  </si>
+  <si>
+    <t>-17.4675-0.0003*B+0.0000*C+0.0718*D+0.0274*E-0.0030*F+0.0000*G+0.8344*H-0.0051*I+0.0313*J-0.0841*K+1.2477*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-17.4675</t>
+  </si>
+  <si>
+    <t>0.0718</t>
+  </si>
+  <si>
+    <t>0.0274</t>
+  </si>
+  <si>
+    <t>0.8344</t>
+  </si>
+  <si>
+    <t>0.0313</t>
+  </si>
+  <si>
+    <t>-0.0841</t>
+  </si>
+  <si>
+    <t>1.2477</t>
+  </si>
+  <si>
+    <t>-18.5795-0.0002*B+0.0000*C+0.0818*D+0.0177*E-0.0016*F+0.0000*G+0.5442*H-0.0086*I+0.0272*J-0.0532*K+1.9433*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-18.5795</t>
+  </si>
+  <si>
+    <t>0.0818</t>
+  </si>
+  <si>
+    <t>0.0177</t>
+  </si>
+  <si>
+    <t>0.5442</t>
+  </si>
+  <si>
+    <t>-0.0532</t>
+  </si>
+  <si>
+    <t>1.9433</t>
+  </si>
+  <si>
+    <t>-29.6809-0.0003*B+0.0000*C+0.1067*D+0.0210*E-0.0029*F+0.0000*G+0.5375*H-0.0113*I+0.0189*J-0.0755*K+1.1419*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-29.6809</t>
+  </si>
+  <si>
+    <t>0.1067</t>
+  </si>
+  <si>
+    <t>0.0210</t>
+  </si>
+  <si>
+    <t>0.5375</t>
+  </si>
+  <si>
+    <t>0.0189</t>
+  </si>
+  <si>
+    <t>-0.0755</t>
+  </si>
+  <si>
+    <t>1.1419</t>
+  </si>
+  <si>
+    <t>-31.2536-0.0005*B+0.0000*C+0.0627*D+0.0090*E-0.0020*F+0.0000*G+0.7238*H-0.0051*I+0.0072*J-0.0971*K+0.9757*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-31.2536</t>
+  </si>
+  <si>
+    <t>0.0090</t>
+  </si>
+  <si>
+    <t>0.7238</t>
+  </si>
+  <si>
+    <t>0.0072</t>
+  </si>
+  <si>
+    <t>-0.0971</t>
+  </si>
+  <si>
+    <t>0.9757</t>
+  </si>
+  <si>
+    <t>-31.2188-0.0004*B+0.0000*C+0.0748*D+0.0088*E-0.0024*F+0.0000*G+1.3807*H-0.0121*I+0.0142*J-0.0999*K+1.5911*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-31.2188</t>
+  </si>
+  <si>
+    <t>0.0748</t>
+  </si>
+  <si>
+    <t>0.0088</t>
+  </si>
+  <si>
+    <t>-0.0121</t>
+  </si>
+  <si>
+    <t>-0.0999</t>
+  </si>
+  <si>
+    <t>1.5911</t>
+  </si>
+  <si>
+    <t>-34.1709-0.0001*B+0.0000*C+0.0642*D+0.0157*E-0.0023*F+0.0000*G+0.8231*H-0.0109*I+0.0195*J-0.0764*K+0.7761*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-34.1709</t>
+  </si>
+  <si>
+    <t>0.0642</t>
+  </si>
+  <si>
+    <t>0.8231</t>
+  </si>
+  <si>
+    <t>-0.0764</t>
+  </si>
+  <si>
+    <t>0.7761</t>
+  </si>
+  <si>
+    <t>-28.3451-0.0004*B+0.0000*C+0.0698*D+0.0090*E-0.0027*F+0.0000*G+0.7215*H-0.0099*I+0.0140*J-0.1133*K+1.8113*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-28.3451</t>
+  </si>
+  <si>
+    <t>0.0698</t>
+  </si>
+  <si>
+    <t>0.7215</t>
+  </si>
+  <si>
+    <t>-0.0099</t>
+  </si>
+  <si>
+    <t>-0.1133</t>
+  </si>
+  <si>
+    <t>1.8113</t>
+  </si>
+  <si>
+    <t>-50.3059-0.0004*B+0.0000*C+0.1011*D+0.0058*E-0.0017*F+0.0000*G+0.7496*H-0.0141*I+0.0327*J-0.0668*K+1.0762*L+1.0858*M</t>
+  </si>
+  <si>
+    <t>-50.3059</t>
+  </si>
+  <si>
+    <t>0.1011</t>
+  </si>
+  <si>
+    <t>0.0058</t>
+  </si>
+  <si>
+    <t>0.7496</t>
+  </si>
+  <si>
+    <t>-0.0141</t>
+  </si>
+  <si>
+    <t>0.0327</t>
+  </si>
+  <si>
+    <t>-0.0668</t>
+  </si>
+  <si>
+    <t>1.0762</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -897,8 +3349,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -908,12 +3361,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{49FCBD75-267D-4264-9EB7-CF2557915C04}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1215,7 +3669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:P121"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="3" max="15" width="9.23046875" style="1"/>
@@ -1973,7 +4427,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2020,7 +4474,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -2067,7 +4521,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2114,7 +4568,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2161,7 +4615,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2208,7 +4662,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2255,7 +4709,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2302,7 +4756,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2349,7 +4803,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2396,7 +4850,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -2443,7 +4897,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -2490,7 +4944,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -2537,7 +4991,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2584,7 +5038,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -2631,7 +5085,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -2678,8 +5132,4328 @@
         <v>186</v>
       </c>
     </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P48" s="1"/>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P49" s="1"/>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P50" s="1"/>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P51" s="1"/>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P52" s="1"/>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P53" s="1"/>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P54" s="1"/>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P55" s="1"/>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P56" s="1"/>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P57" s="1"/>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P58" s="1"/>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P59" s="1"/>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P60" s="1"/>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P61" s="1"/>
+    </row>
+    <row r="62" spans="1:16">
+      <c r="A62" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P62" s="1"/>
+    </row>
+    <row r="63" spans="1:16">
+      <c r="A63" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P63" s="1"/>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P64" s="1"/>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P65" s="1"/>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P66" s="1"/>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P67" s="1"/>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P68" s="1"/>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P69" s="1"/>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P70" s="1"/>
+    </row>
+    <row r="71" spans="1:16">
+      <c r="A71" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P71" s="1"/>
+    </row>
+    <row r="72" spans="1:16">
+      <c r="A72" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P72" s="1"/>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="A73" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P73" s="1"/>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="A74" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P74" s="1"/>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P75" s="1"/>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P76" s="1"/>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P77" s="1"/>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="A78" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P78" s="1"/>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="A79" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P79" s="1"/>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P80" s="1"/>
+    </row>
+    <row r="81" spans="1:16">
+      <c r="A81" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P81" s="1"/>
+    </row>
+    <row r="82" spans="1:16">
+      <c r="A82" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P82" s="1"/>
+    </row>
+    <row r="83" spans="1:16">
+      <c r="A83" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P83" s="1"/>
+    </row>
+    <row r="84" spans="1:16">
+      <c r="A84" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P84" s="1"/>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="A85" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P85" s="1"/>
+    </row>
+    <row r="86" spans="1:16">
+      <c r="A86" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P86" s="1"/>
+    </row>
+    <row r="87" spans="1:16">
+      <c r="A87" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P87" s="1"/>
+    </row>
+    <row r="88" spans="1:16">
+      <c r="A88" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P88" s="1"/>
+    </row>
+    <row r="89" spans="1:16">
+      <c r="A89" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P89" s="1"/>
+    </row>
+    <row r="90" spans="1:16">
+      <c r="A90" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P90" s="1"/>
+    </row>
+    <row r="91" spans="1:16">
+      <c r="A91" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P91" s="1"/>
+    </row>
+    <row r="92" spans="1:16">
+      <c r="A92" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P92" s="1"/>
+    </row>
+    <row r="93" spans="1:16">
+      <c r="A93" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P93" s="1"/>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="A94" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P94" s="1"/>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="A95" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P95" s="1"/>
+    </row>
+    <row r="96" spans="1:16">
+      <c r="A96" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P96" s="1"/>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="A97" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P97" s="1"/>
+    </row>
+    <row r="98" spans="1:16">
+      <c r="A98" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P98" s="1"/>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P99" s="1"/>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P100" s="1"/>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P101" s="1"/>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P102" s="1"/>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P103" s="1"/>
+    </row>
+    <row r="104" spans="1:16">
+      <c r="A104" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P104" s="1"/>
+    </row>
+    <row r="105" spans="1:16">
+      <c r="A105" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="M105" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P105" s="1"/>
+    </row>
+    <row r="106" spans="1:16">
+      <c r="A106" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P106" s="1"/>
+    </row>
+    <row r="107" spans="1:16">
+      <c r="A107" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P107" s="1"/>
+    </row>
+    <row r="108" spans="1:16">
+      <c r="A108" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P108" s="1"/>
+    </row>
+    <row r="109" spans="1:16">
+      <c r="A109" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P109" s="1"/>
+    </row>
+    <row r="110" spans="1:16">
+      <c r="A110" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P110" s="1"/>
+    </row>
+    <row r="111" spans="1:16">
+      <c r="A111" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="N111" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P111" s="1"/>
+    </row>
+    <row r="112" spans="1:16">
+      <c r="A112" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="N112" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P112" s="1"/>
+    </row>
+    <row r="113" spans="1:16">
+      <c r="A113" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="N113" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P113" s="1"/>
+    </row>
+    <row r="114" spans="1:16">
+      <c r="A114" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="M114" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P114" s="1"/>
+    </row>
+    <row r="115" spans="1:16">
+      <c r="A115" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P115" s="1"/>
+    </row>
+    <row r="116" spans="1:16">
+      <c r="A116" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P116" s="1"/>
+    </row>
+    <row r="117" spans="1:16">
+      <c r="A117" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="N117" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P117" s="1"/>
+    </row>
+    <row r="118" spans="1:16">
+      <c r="A118" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="N118" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P118" s="1"/>
+    </row>
+    <row r="119" spans="1:16">
+      <c r="A119" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="N119" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P119" s="1"/>
+    </row>
+    <row r="120" spans="1:16">
+      <c r="A120" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P120" s="1"/>
+    </row>
+    <row r="121" spans="1:16">
+      <c r="A121" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P121" s="1"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/mainWidget/mainWidget/src/database/计算模型-慢速烤燃试验.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-慢速烤燃试验.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5ED57F-91CE-472D-9253-84BD3A3382BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A3F2C3-FD2F-4480-B8B3-1E180047A6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5145,8 +5145,8 @@
       <c r="D32" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>231</v>
+      <c r="E32" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>232</v>
@@ -5157,8 +5157,8 @@
       <c r="H32" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>231</v>
+      <c r="I32" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>235</v>
@@ -5193,8 +5193,8 @@
       <c r="D33" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>231</v>
+      <c r="E33" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>244</v>
@@ -5205,8 +5205,8 @@
       <c r="H33" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>231</v>
+      <c r="I33" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>247</v>
@@ -5241,8 +5241,8 @@
       <c r="D34" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>231</v>
+      <c r="E34" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>255</v>
@@ -5253,8 +5253,8 @@
       <c r="H34" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>231</v>
+      <c r="I34" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>258</v>
@@ -5289,8 +5289,8 @@
       <c r="D35" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>231</v>
+      <c r="E35" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>265</v>
@@ -5301,8 +5301,8 @@
       <c r="H35" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>231</v>
+      <c r="I35" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>267</v>
@@ -5337,8 +5337,8 @@
       <c r="D36" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>231</v>
+      <c r="E36" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>275</v>
@@ -5349,8 +5349,8 @@
       <c r="H36" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>231</v>
+      <c r="I36" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>278</v>
@@ -5385,8 +5385,8 @@
       <c r="D37" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>231</v>
+      <c r="E37" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>255</v>
@@ -5397,8 +5397,8 @@
       <c r="H37" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>231</v>
+      <c r="I37" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>288</v>
@@ -5433,8 +5433,8 @@
       <c r="D38" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>231</v>
+      <c r="E38" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>295</v>
@@ -5445,8 +5445,8 @@
       <c r="H38" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>231</v>
+      <c r="I38" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>297</v>
@@ -5481,8 +5481,8 @@
       <c r="D39" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>231</v>
+      <c r="E39" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>304</v>
@@ -5493,8 +5493,8 @@
       <c r="H39" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>231</v>
+      <c r="I39" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>306</v>
@@ -5529,8 +5529,8 @@
       <c r="D40" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>231</v>
+      <c r="E40" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>312</v>
@@ -5541,8 +5541,8 @@
       <c r="H40" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>231</v>
+      <c r="I40" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>315</v>
@@ -5577,8 +5577,8 @@
       <c r="D41" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>231</v>
+      <c r="E41" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>255</v>
@@ -5589,8 +5589,8 @@
       <c r="H41" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>231</v>
+      <c r="I41" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>324</v>
@@ -5625,8 +5625,8 @@
       <c r="D42" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>231</v>
+      <c r="E42" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>331</v>
@@ -5637,8 +5637,8 @@
       <c r="H42" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>231</v>
+      <c r="I42" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>334</v>
@@ -5673,8 +5673,8 @@
       <c r="D43" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>231</v>
+      <c r="E43" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>341</v>
@@ -5685,8 +5685,8 @@
       <c r="H43" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>231</v>
+      <c r="I43" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>343</v>
@@ -5721,8 +5721,8 @@
       <c r="D44" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>231</v>
+      <c r="E44" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>350</v>
@@ -5733,8 +5733,8 @@
       <c r="H44" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>231</v>
+      <c r="I44" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>352</v>
@@ -5769,8 +5769,8 @@
       <c r="D45" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>231</v>
+      <c r="E45" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>359</v>
@@ -5781,8 +5781,8 @@
       <c r="H45" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>231</v>
+      <c r="I45" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>361</v>
@@ -5817,8 +5817,8 @@
       <c r="D46" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>231</v>
+      <c r="E46" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>368</v>
@@ -5829,8 +5829,8 @@
       <c r="H46" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>231</v>
+      <c r="I46" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>370</v>
@@ -5865,8 +5865,8 @@
       <c r="D47" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>231</v>
+      <c r="E47" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>377</v>
@@ -5877,8 +5877,8 @@
       <c r="H47" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>231</v>
+      <c r="I47" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>379</v>
@@ -5913,8 +5913,8 @@
       <c r="D48" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>231</v>
+      <c r="E48" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>386</v>
@@ -5925,8 +5925,8 @@
       <c r="H48" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>231</v>
+      <c r="I48" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>388</v>
@@ -5961,8 +5961,8 @@
       <c r="D49" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>231</v>
+      <c r="E49" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>255</v>
@@ -5973,8 +5973,8 @@
       <c r="H49" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>231</v>
+      <c r="I49" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>395</v>
@@ -6009,8 +6009,8 @@
       <c r="D50" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>231</v>
+      <c r="E50" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>401</v>
@@ -6021,8 +6021,8 @@
       <c r="H50" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>231</v>
+      <c r="I50" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>403</v>
@@ -6057,8 +6057,8 @@
       <c r="D51" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>231</v>
+      <c r="E51" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>410</v>
@@ -6069,8 +6069,8 @@
       <c r="H51" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>231</v>
+      <c r="I51" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>411</v>
@@ -6105,8 +6105,8 @@
       <c r="D52" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>231</v>
+      <c r="E52" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>417</v>
@@ -6117,8 +6117,8 @@
       <c r="H52" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>231</v>
+      <c r="I52" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>420</v>
@@ -6153,8 +6153,8 @@
       <c r="D53" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>231</v>
+      <c r="E53" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>427</v>
@@ -6165,8 +6165,8 @@
       <c r="H53" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>231</v>
+      <c r="I53" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>429</v>
@@ -6201,8 +6201,8 @@
       <c r="D54" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>231</v>
+      <c r="E54" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>386</v>
@@ -6213,8 +6213,8 @@
       <c r="H54" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>231</v>
+      <c r="I54" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>436</v>
@@ -6249,8 +6249,8 @@
       <c r="D55" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>231</v>
+      <c r="E55" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>295</v>
@@ -6261,8 +6261,8 @@
       <c r="H55" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>231</v>
+      <c r="I55" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>444</v>
@@ -6297,8 +6297,8 @@
       <c r="D56" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>231</v>
+      <c r="E56" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>450</v>
@@ -6309,8 +6309,8 @@
       <c r="H56" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>231</v>
+      <c r="I56" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>452</v>
@@ -6345,8 +6345,8 @@
       <c r="D57" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>231</v>
+      <c r="E57" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>459</v>
@@ -6357,8 +6357,8 @@
       <c r="H57" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>231</v>
+      <c r="I57" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>461</v>
@@ -6393,8 +6393,8 @@
       <c r="D58" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>231</v>
+      <c r="E58" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>255</v>
@@ -6405,8 +6405,8 @@
       <c r="H58" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>231</v>
+      <c r="I58" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>470</v>
@@ -6441,8 +6441,8 @@
       <c r="D59" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>231</v>
+      <c r="E59" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>478</v>
@@ -6453,8 +6453,8 @@
       <c r="H59" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>231</v>
+      <c r="I59" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>480</v>
@@ -6489,8 +6489,8 @@
       <c r="D60" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>231</v>
+      <c r="E60" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>486</v>
@@ -6501,8 +6501,8 @@
       <c r="H60" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>231</v>
+      <c r="I60" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>488</v>
@@ -6537,8 +6537,8 @@
       <c r="D61" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>231</v>
+      <c r="E61" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>495</v>
@@ -6549,8 +6549,8 @@
       <c r="H61" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>231</v>
+      <c r="I61" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>497</v>
@@ -6585,8 +6585,8 @@
       <c r="D62" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>231</v>
+      <c r="E62" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>255</v>
@@ -6597,8 +6597,8 @@
       <c r="H62" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>231</v>
+      <c r="I62" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>504</v>
@@ -6633,8 +6633,8 @@
       <c r="D63" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>231</v>
+      <c r="E63" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>511</v>
@@ -6645,8 +6645,8 @@
       <c r="H63" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>231</v>
+      <c r="I63" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>513</v>
@@ -6681,8 +6681,8 @@
       <c r="D64" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>231</v>
+      <c r="E64" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>521</v>
@@ -6693,8 +6693,8 @@
       <c r="H64" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>231</v>
+      <c r="I64" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>523</v>
@@ -6729,8 +6729,8 @@
       <c r="D65" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>231</v>
+      <c r="E65" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>529</v>
@@ -6741,8 +6741,8 @@
       <c r="H65" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>231</v>
+      <c r="I65" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>532</v>
@@ -6777,8 +6777,8 @@
       <c r="D66" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>231</v>
+      <c r="E66" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>539</v>
@@ -6789,8 +6789,8 @@
       <c r="H66" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="I66" s="1" t="s">
-        <v>231</v>
+      <c r="I66" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>542</v>
@@ -6825,8 +6825,8 @@
       <c r="D67" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>231</v>
+      <c r="E67" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>548</v>
@@ -6837,8 +6837,8 @@
       <c r="H67" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>231</v>
+      <c r="I67" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>551</v>
@@ -6873,8 +6873,8 @@
       <c r="D68" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>231</v>
+      <c r="E68" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>558</v>
@@ -6885,8 +6885,8 @@
       <c r="H68" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>231</v>
+      <c r="I68" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>560</v>
@@ -6921,8 +6921,8 @@
       <c r="D69" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>231</v>
+      <c r="E69" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>566</v>
@@ -6933,8 +6933,8 @@
       <c r="H69" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>231</v>
+      <c r="I69" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>568</v>
@@ -6969,8 +6969,8 @@
       <c r="D70" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>231</v>
+      <c r="E70" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>574</v>
@@ -6981,8 +6981,8 @@
       <c r="H70" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>231</v>
+      <c r="I70" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>576</v>
@@ -7017,8 +7017,8 @@
       <c r="D71" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>231</v>
+      <c r="E71" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>584</v>
@@ -7029,8 +7029,8 @@
       <c r="H71" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>231</v>
+      <c r="I71" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>586</v>
@@ -7065,8 +7065,8 @@
       <c r="D72" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>231</v>
+      <c r="E72" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>592</v>
@@ -7077,8 +7077,8 @@
       <c r="H72" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>231</v>
+      <c r="I72" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>594</v>
@@ -7113,8 +7113,8 @@
       <c r="D73" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>231</v>
+      <c r="E73" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>599</v>
@@ -7125,8 +7125,8 @@
       <c r="H73" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>231</v>
+      <c r="I73" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>600</v>
@@ -7161,8 +7161,8 @@
       <c r="D74" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>231</v>
+      <c r="E74" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>607</v>
@@ -7173,8 +7173,8 @@
       <c r="H74" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>231</v>
+      <c r="I74" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>609</v>
@@ -7209,8 +7209,8 @@
       <c r="D75" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>231</v>
+      <c r="E75" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>615</v>
@@ -7221,8 +7221,8 @@
       <c r="H75" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>231</v>
+      <c r="I75" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>616</v>
@@ -7257,8 +7257,8 @@
       <c r="D76" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>231</v>
+      <c r="E76" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>622</v>
@@ -7269,8 +7269,8 @@
       <c r="H76" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>231</v>
+      <c r="I76" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>623</v>
@@ -7305,8 +7305,8 @@
       <c r="D77" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>231</v>
+      <c r="E77" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>630</v>
@@ -7317,8 +7317,8 @@
       <c r="H77" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>231</v>
+      <c r="I77" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>632</v>
@@ -7353,8 +7353,8 @@
       <c r="D78" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>231</v>
+      <c r="E78" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>255</v>
@@ -7365,8 +7365,8 @@
       <c r="H78" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I78" s="1" t="s">
-        <v>231</v>
+      <c r="I78" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>638</v>
@@ -7401,8 +7401,8 @@
       <c r="D79" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>231</v>
+      <c r="E79" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>645</v>
@@ -7413,8 +7413,8 @@
       <c r="H79" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="I79" s="1" t="s">
-        <v>231</v>
+      <c r="I79" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>315</v>
@@ -7449,8 +7449,8 @@
       <c r="D80" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>231</v>
+      <c r="E80" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>651</v>
@@ -7461,8 +7461,8 @@
       <c r="H80" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="I80" s="1" t="s">
-        <v>231</v>
+      <c r="I80" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>652</v>
@@ -7497,8 +7497,8 @@
       <c r="D81" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>231</v>
+      <c r="E81" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>657</v>
@@ -7509,8 +7509,8 @@
       <c r="H81" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="I81" s="1" t="s">
-        <v>231</v>
+      <c r="I81" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>659</v>
@@ -7545,8 +7545,8 @@
       <c r="D82" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>231</v>
+      <c r="E82" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>664</v>
@@ -7557,8 +7557,8 @@
       <c r="H82" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I82" s="1" t="s">
-        <v>231</v>
+      <c r="I82" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>665</v>
@@ -7593,8 +7593,8 @@
       <c r="D83" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>231</v>
+      <c r="E83" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>521</v>
@@ -7605,8 +7605,8 @@
       <c r="H83" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="I83" s="1" t="s">
-        <v>231</v>
+      <c r="I83" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>671</v>
@@ -7641,8 +7641,8 @@
       <c r="D84" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>231</v>
+      <c r="E84" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>678</v>
@@ -7653,8 +7653,8 @@
       <c r="H84" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>231</v>
+      <c r="I84" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>679</v>
@@ -7689,8 +7689,8 @@
       <c r="D85" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>231</v>
+      <c r="E85" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>255</v>
@@ -7701,8 +7701,8 @@
       <c r="H85" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I85" s="1" t="s">
-        <v>231</v>
+      <c r="I85" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>685</v>
@@ -7737,8 +7737,8 @@
       <c r="D86" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>231</v>
+      <c r="E86" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>691</v>
@@ -7749,8 +7749,8 @@
       <c r="H86" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I86" s="1" t="s">
-        <v>231</v>
+      <c r="I86" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>315</v>
@@ -7785,8 +7785,8 @@
       <c r="D87" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>231</v>
+      <c r="E87" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>696</v>
@@ -7797,8 +7797,8 @@
       <c r="H87" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I87" s="1" t="s">
-        <v>231</v>
+      <c r="I87" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>698</v>
@@ -7833,8 +7833,8 @@
       <c r="D88" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>231</v>
+      <c r="E88" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>705</v>
@@ -7845,8 +7845,8 @@
       <c r="H88" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="I88" s="1" t="s">
-        <v>231</v>
+      <c r="I88" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>706</v>
@@ -7881,8 +7881,8 @@
       <c r="D89" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>231</v>
+      <c r="E89" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>713</v>
@@ -7893,8 +7893,8 @@
       <c r="H89" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I89" s="1" t="s">
-        <v>231</v>
+      <c r="I89" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>715</v>
@@ -7929,8 +7929,8 @@
       <c r="D90" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>231</v>
+      <c r="E90" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>721</v>
@@ -7941,8 +7941,8 @@
       <c r="H90" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="I90" s="1" t="s">
-        <v>231</v>
+      <c r="I90" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>724</v>
@@ -7977,8 +7977,8 @@
       <c r="D91" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>231</v>
+      <c r="E91" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>729</v>
@@ -7989,8 +7989,8 @@
       <c r="H91" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>231</v>
+      <c r="I91" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>315</v>
@@ -8025,8 +8025,8 @@
       <c r="D92" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>231</v>
+      <c r="E92" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>735</v>
@@ -8037,8 +8037,8 @@
       <c r="H92" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I92" s="1" t="s">
-        <v>231</v>
+      <c r="I92" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>736</v>
@@ -8073,8 +8073,8 @@
       <c r="D93" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>231</v>
+      <c r="E93" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>743</v>
@@ -8085,8 +8085,8 @@
       <c r="H93" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="I93" s="1" t="s">
-        <v>231</v>
+      <c r="I93" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>744</v>
@@ -8121,8 +8121,8 @@
       <c r="D94" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>231</v>
+      <c r="E94" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>751</v>
@@ -8133,8 +8133,8 @@
       <c r="H94" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="I94" s="1" t="s">
-        <v>231</v>
+      <c r="I94" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>753</v>
@@ -8169,8 +8169,8 @@
       <c r="D95" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>231</v>
+      <c r="E95" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>255</v>
@@ -8181,8 +8181,8 @@
       <c r="H95" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I95" s="1" t="s">
-        <v>231</v>
+      <c r="I95" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>759</v>
@@ -8217,8 +8217,8 @@
       <c r="D96" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>231</v>
+      <c r="E96" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>765</v>
@@ -8229,8 +8229,8 @@
       <c r="H96" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I96" s="1" t="s">
-        <v>231</v>
+      <c r="I96" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>767</v>
@@ -8265,8 +8265,8 @@
       <c r="D97" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>231</v>
+      <c r="E97" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>773</v>
@@ -8277,8 +8277,8 @@
       <c r="H97" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I97" s="1" t="s">
-        <v>231</v>
+      <c r="I97" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>775</v>
@@ -8313,8 +8313,8 @@
       <c r="D98" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>231</v>
+      <c r="E98" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>781</v>
@@ -8325,8 +8325,8 @@
       <c r="H98" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>231</v>
+      <c r="I98" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>782</v>
@@ -8361,8 +8361,8 @@
       <c r="D99" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>231</v>
+      <c r="E99" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>574</v>
@@ -8373,8 +8373,8 @@
       <c r="H99" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="I99" s="1" t="s">
-        <v>231</v>
+      <c r="I99" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>788</v>
@@ -8409,8 +8409,8 @@
       <c r="D100" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>231</v>
+      <c r="E100" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>795</v>
@@ -8421,8 +8421,8 @@
       <c r="H100" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="I100" s="1" t="s">
-        <v>231</v>
+      <c r="I100" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>796</v>
@@ -8457,8 +8457,8 @@
       <c r="D101" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>231</v>
+      <c r="E101" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>803</v>
@@ -8469,8 +8469,8 @@
       <c r="H101" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="I101" s="1" t="s">
-        <v>231</v>
+      <c r="I101" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>805</v>
@@ -8505,8 +8505,8 @@
       <c r="D102" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>231</v>
+      <c r="E102" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>812</v>
@@ -8517,8 +8517,8 @@
       <c r="H102" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I102" s="1" t="s">
-        <v>231</v>
+      <c r="I102" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>814</v>
@@ -8553,8 +8553,8 @@
       <c r="D103" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>231</v>
+      <c r="E103" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>820</v>
@@ -8565,8 +8565,8 @@
       <c r="H103" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I103" s="1" t="s">
-        <v>231</v>
+      <c r="I103" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>821</v>
@@ -8601,8 +8601,8 @@
       <c r="D104" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>231</v>
+      <c r="E104" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>827</v>
@@ -8613,8 +8613,8 @@
       <c r="H104" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="I104" s="1" t="s">
-        <v>231</v>
+      <c r="I104" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>829</v>
@@ -8649,8 +8649,8 @@
       <c r="D105" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>231</v>
+      <c r="E105" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>275</v>
@@ -8661,8 +8661,8 @@
       <c r="H105" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="I105" s="1" t="s">
-        <v>231</v>
+      <c r="I105" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>837</v>
@@ -8697,8 +8697,8 @@
       <c r="D106" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>231</v>
+      <c r="E106" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>843</v>
@@ -8709,8 +8709,8 @@
       <c r="H106" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="I106" s="1" t="s">
-        <v>231</v>
+      <c r="I106" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>844</v>
@@ -8745,8 +8745,8 @@
       <c r="D107" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>231</v>
+      <c r="E107" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>850</v>
@@ -8757,8 +8757,8 @@
       <c r="H107" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I107" s="1" t="s">
-        <v>231</v>
+      <c r="I107" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J107" s="1" t="s">
         <v>852</v>
@@ -8793,8 +8793,8 @@
       <c r="D108" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>231</v>
+      <c r="E108" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>255</v>
@@ -8805,8 +8805,8 @@
       <c r="H108" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I108" s="1" t="s">
-        <v>231</v>
+      <c r="I108" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>857</v>
@@ -8841,8 +8841,8 @@
       <c r="D109" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>231</v>
+      <c r="E109" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>863</v>
@@ -8853,8 +8853,8 @@
       <c r="H109" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I109" s="1" t="s">
-        <v>231</v>
+      <c r="I109" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>865</v>
@@ -8889,8 +8889,8 @@
       <c r="D110" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>231</v>
+      <c r="E110" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>870</v>
@@ -8901,8 +8901,8 @@
       <c r="H110" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I110" s="1" t="s">
-        <v>231</v>
+      <c r="I110" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>871</v>
@@ -8937,8 +8937,8 @@
       <c r="D111" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>231</v>
+      <c r="E111" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>876</v>
@@ -8949,8 +8949,8 @@
       <c r="H111" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="I111" s="1" t="s">
-        <v>231</v>
+      <c r="I111" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J111" s="1" t="s">
         <v>877</v>
@@ -8985,8 +8985,8 @@
       <c r="D112" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>231</v>
+      <c r="E112" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>883</v>
@@ -8997,8 +8997,8 @@
       <c r="H112" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I112" s="1" t="s">
-        <v>231</v>
+      <c r="I112" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>885</v>
@@ -9033,8 +9033,8 @@
       <c r="D113" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>231</v>
+      <c r="E113" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>548</v>
@@ -9045,8 +9045,8 @@
       <c r="H113" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="I113" s="1" t="s">
-        <v>231</v>
+      <c r="I113" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J113" s="1" t="s">
         <v>315</v>
@@ -9081,8 +9081,8 @@
       <c r="D114" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>231</v>
+      <c r="E114" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>896</v>
@@ -9093,8 +9093,8 @@
       <c r="H114" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I114" s="1" t="s">
-        <v>231</v>
+      <c r="I114" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J114" s="1" t="s">
         <v>898</v>
@@ -9129,8 +9129,8 @@
       <c r="D115" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>231</v>
+      <c r="E115" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>904</v>
@@ -9141,8 +9141,8 @@
       <c r="H115" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="I115" s="1" t="s">
-        <v>231</v>
+      <c r="I115" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J115" s="1" t="s">
         <v>906</v>
@@ -9177,8 +9177,8 @@
       <c r="D116" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>231</v>
+      <c r="E116" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>911</v>
@@ -9189,8 +9189,8 @@
       <c r="H116" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="I116" s="1" t="s">
-        <v>231</v>
+      <c r="I116" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J116" s="1" t="s">
         <v>913</v>
@@ -9225,8 +9225,8 @@
       <c r="D117" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>231</v>
+      <c r="E117" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>265</v>
@@ -9237,8 +9237,8 @@
       <c r="H117" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="I117" s="1" t="s">
-        <v>231</v>
+      <c r="I117" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J117" s="1" t="s">
         <v>920</v>
@@ -9273,8 +9273,8 @@
       <c r="D118" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>231</v>
+      <c r="E118" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>926</v>
@@ -9285,8 +9285,8 @@
       <c r="H118" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I118" s="1" t="s">
-        <v>231</v>
+      <c r="I118" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J118" s="1" t="s">
         <v>523</v>
@@ -9321,8 +9321,8 @@
       <c r="D119" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>231</v>
+      <c r="E119" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>933</v>
@@ -9333,8 +9333,8 @@
       <c r="H119" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I119" s="1" t="s">
-        <v>231</v>
+      <c r="I119" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J119" s="1" t="s">
         <v>934</v>
@@ -9369,8 +9369,8 @@
       <c r="D120" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>231</v>
+      <c r="E120" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>939</v>
@@ -9381,8 +9381,8 @@
       <c r="H120" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I120" s="1" t="s">
-        <v>231</v>
+      <c r="I120" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J120" s="1" t="s">
         <v>940</v>
@@ -9417,8 +9417,8 @@
       <c r="D121" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>231</v>
+      <c r="E121" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>946</v>
@@ -9429,8 +9429,8 @@
       <c r="H121" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I121" s="1" t="s">
-        <v>231</v>
+      <c r="I121" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="J121" s="1" t="s">
         <v>948</v>

--- a/mainWidget/mainWidget/src/database/计算模型-慢速烤燃试验.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-慢速烤燃试验.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A3F2C3-FD2F-4480-B8B3-1E180047A6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="22155" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -154,9 +148,6 @@
     <t>L (mm)</t>
   </si>
   <si>
-    <t>M (mm)</t>
-  </si>
-  <si>
     <t>-3.2932-0.0000*B+0.0000*C+0.0505*D+0.0008*E-0.0021*F+0.0000*G+0.2542*H-0.0047*I+0.0066*J-0.0414*K+0.2398*L+1.0038*M</t>
   </si>
   <si>
@@ -3302,13 +3293,35 @@
   </si>
   <si>
     <t>120</t>
+  </si>
+  <si>
+    <r>
+      <t>M (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3330,6 +3343,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3353,7 +3372,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3364,10 +3383,13 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{49FCBD75-267D-4264-9EB7-CF2557915C04}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3383,9 +3405,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3423,7 +3445,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3495,7 +3517,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3668,11 +3690,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P121"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="15" width="9.23046875" style="1"/>
+    <col min="3" max="15" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -3718,8 +3740,8 @@
       <c r="N1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>44</v>
+      <c r="O1" s="4" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -3727,46 +3749,46 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -3774,46 +3796,46 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -3821,46 +3843,46 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L4" s="2">
         <v>2.2700000000000001E-2</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -3868,46 +3890,46 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -3915,46 +3937,46 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -3962,46 +3984,46 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -4009,43 +4031,43 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O8" s="2">
         <v>0.99109999999999998</v>
@@ -4056,46 +4078,46 @@
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -4103,46 +4125,46 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -4150,46 +4172,46 @@
         <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -4197,46 +4219,46 @@
         <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -4244,46 +4266,46 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -4291,46 +4313,46 @@
         <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -4338,46 +4360,46 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -4385,46 +4407,46 @@
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I16" s="2">
         <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -4432,46 +4454,46 @@
         <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I17" s="2">
         <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -4479,46 +4501,46 @@
         <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I18" s="2">
         <v>0</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -4526,46 +4548,46 @@
         <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -4573,46 +4595,46 @@
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I20" s="2">
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -4620,46 +4642,46 @@
         <v>22</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2">
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -4667,46 +4689,46 @@
         <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -4714,46 +4736,46 @@
         <v>24</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -4761,46 +4783,46 @@
         <v>25</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -4808,46 +4830,46 @@
         <v>26</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -4855,46 +4877,46 @@
         <v>27</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -4902,46 +4924,46 @@
         <v>28</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="O27" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -4949,46 +4971,46 @@
         <v>29</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I28" s="2">
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -4996,46 +5018,46 @@
         <v>30</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -5043,46 +5065,46 @@
         <v>31</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I30" s="2">
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -5090,4370 +5112,4371 @@
         <v>32</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I31" s="2">
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N31" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="O31" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="I32" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J32" s="1" t="s">
+      <c r="K32" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="M32" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="O32" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="P32" s="1"/>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="I33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J33" s="1" t="s">
+      <c r="K33" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="M33" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="N33" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="N33" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="O33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P33" s="1"/>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J34" s="1" t="s">
+      <c r="K34" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="M34" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="N34" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="N34" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="O34" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="H35" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J35" s="1" t="s">
+      <c r="K35" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="M35" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="N35" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="N35" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="O35" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P35" s="1"/>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J36" s="1" t="s">
+      <c r="K36" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="M36" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="N36" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="N36" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="O36" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J37" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="L37" s="1" t="s">
+      <c r="M37" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="M37" s="1" t="s">
+      <c r="N37" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="N37" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="O37" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="M38" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="N38" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="N38" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="O38" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="H39" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J39" s="1" t="s">
+      <c r="K39" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L39" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="L39" s="1" t="s">
+      <c r="M39" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="M39" s="1" t="s">
+      <c r="N39" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="N39" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="O39" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J40" s="1" t="s">
+      <c r="K40" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="M40" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="N40" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="N40" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="O40" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="M41" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="N41" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="N41" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="O41" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="I42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J42" s="1" t="s">
+      <c r="K42" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="M42" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="M42" s="1" t="s">
+      <c r="N42" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="N42" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="O42" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H43" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J43" s="1" t="s">
+      <c r="K43" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="M43" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="M43" s="1" t="s">
+      <c r="N43" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="N43" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="O43" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J44" s="1" t="s">
+      <c r="K44" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="L44" s="1" t="s">
+      <c r="M44" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="M44" s="1" t="s">
+      <c r="N44" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="N44" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="O44" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="H45" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J45" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="M45" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="N45" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="N45" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="O45" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J46" s="1" t="s">
+      <c r="K46" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="L46" s="1" t="s">
+      <c r="M46" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="M46" s="1" t="s">
+      <c r="N46" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="N46" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="O46" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J47" s="1" t="s">
+      <c r="K47" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="M47" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="N47" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="N47" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="O47" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F48" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J48" s="1" t="s">
+      <c r="K48" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L48" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L48" s="1" t="s">
+      <c r="M48" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="M48" s="1" t="s">
+      <c r="N48" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="N48" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="O48" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G49" s="1" t="s">
+      <c r="H49" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J49" s="1" t="s">
+      <c r="K49" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L49" s="1" t="s">
+      <c r="M49" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="N49" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="N49" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="O49" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F50" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="H50" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J50" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="L50" s="1" t="s">
+      <c r="M50" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="M50" s="1" t="s">
+      <c r="N50" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="N50" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="O50" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="G51" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J51" s="1" t="s">
+      <c r="K51" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="L51" s="1" t="s">
+      <c r="M51" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="M51" s="1" t="s">
+      <c r="N51" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="N51" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="O51" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P51" s="1"/>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="I52" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J52" s="1" t="s">
+      <c r="K52" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="M52" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="N52" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="N52" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="O52" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P52" s="1"/>
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H53" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J53" s="1" t="s">
+      <c r="K53" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="M53" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="M53" s="1" t="s">
+      <c r="N53" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="N53" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="O53" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P53" s="1"/>
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="G54" s="1" t="s">
+      <c r="H54" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J54" s="1" t="s">
+      <c r="K54" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="L54" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="N54" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="N54" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="O54" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P54" s="1"/>
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F55" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="I55" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="H55" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J55" s="1" t="s">
+      <c r="K55" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="L55" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="M55" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="L55" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M55" s="1" t="s">
+      <c r="N55" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="N55" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="O55" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P55" s="1"/>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F56" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="H56" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J56" s="1" t="s">
+      <c r="K56" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="L56" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="M56" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="N56" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="N56" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="O56" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P56" s="1"/>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F57" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="H57" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J57" s="1" t="s">
+      <c r="K57" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="L57" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="L57" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="N57" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="N57" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="O57" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P57" s="1"/>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="I58" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J58" s="1" t="s">
+      <c r="K58" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="L58" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="L58" s="1" t="s">
+      <c r="M58" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="N58" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="N58" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="O58" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P58" s="1"/>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F59" s="1" t="s">
+      <c r="G59" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="H59" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J59" s="1" t="s">
+      <c r="K59" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="L59" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M59" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="L59" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="M59" s="1" t="s">
+      <c r="N59" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="N59" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="O59" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P59" s="1"/>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F60" s="1" t="s">
+      <c r="G60" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="H60" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J60" s="1" t="s">
+      <c r="K60" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="L60" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="L60" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="N60" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="N60" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="O60" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P60" s="1"/>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F61" s="1" t="s">
+      <c r="G61" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="H61" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J61" s="1" t="s">
+      <c r="K61" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="L61" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M61" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="L61" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="M61" s="1" t="s">
+      <c r="N61" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="N61" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="O61" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P61" s="1"/>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G62" s="1" t="s">
+      <c r="H62" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J62" s="1" t="s">
+      <c r="K62" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="L62" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="L62" s="1" t="s">
+      <c r="M62" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="M62" s="1" t="s">
+      <c r="N62" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="N62" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="O62" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P62" s="1"/>
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F63" s="1" t="s">
+      <c r="G63" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="H63" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J63" s="1" t="s">
+      <c r="K63" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="L63" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="L63" s="1" t="s">
+      <c r="M63" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="N63" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="N63" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="O63" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P63" s="1"/>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F64" s="1" t="s">
+      <c r="G64" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="H64" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="L64" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="L64" s="1" t="s">
+      <c r="M64" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="M64" s="1" t="s">
+      <c r="N64" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="N64" s="1" t="s">
-        <v>527</v>
-      </c>
       <c r="O64" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P64" s="1"/>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F65" s="1" t="s">
+      <c r="G65" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="H65" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="I65" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="I65" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J65" s="1" t="s">
+      <c r="K65" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="L65" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L65" s="1" t="s">
+      <c r="M65" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="M65" s="1" t="s">
+      <c r="N65" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="N65" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="O65" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P65" s="1"/>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F66" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="H66" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="I66" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J66" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="L66" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M66" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="L66" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="M66" s="1" t="s">
+      <c r="N66" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="N66" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="O66" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P66" s="1"/>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F67" s="1" t="s">
+      <c r="G67" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="H67" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="I67" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="I67" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J67" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="L67" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="L67" s="1" t="s">
+      <c r="M67" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="M67" s="1" t="s">
+      <c r="N67" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="N67" s="1" t="s">
-        <v>555</v>
-      </c>
       <c r="O67" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P67" s="1"/>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F68" s="1" t="s">
+      <c r="G68" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="H68" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J68" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J68" s="1" t="s">
+      <c r="K68" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="L68" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="L68" s="1" t="s">
+      <c r="M68" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N68" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="O68" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P68" s="1"/>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F69" s="1" t="s">
+      <c r="G69" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="H69" s="1" t="s">
+      <c r="I69" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I69" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J69" s="1" t="s">
+      <c r="K69" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L69" s="1" t="s">
+      <c r="M69" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="N69" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="N69" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="O69" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P69" s="1"/>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F70" s="1" t="s">
+      <c r="G70" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="H70" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="L70" s="1" t="s">
+      <c r="M70" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="N70" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="N70" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="O70" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P70" s="1"/>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="E71" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F71" s="1" t="s">
+      <c r="G71" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="H71" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J71" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="H71" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J71" s="1" t="s">
+      <c r="K71" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L71" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="K71" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L71" s="1" t="s">
+      <c r="M71" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="M71" s="1" t="s">
+      <c r="N71" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="N71" s="1" t="s">
-        <v>589</v>
-      </c>
       <c r="O71" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P71" s="1"/>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F72" s="1" t="s">
+      <c r="G72" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="H72" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J72" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J72" s="1" t="s">
+      <c r="K72" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="M72" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="M72" s="1" t="s">
+      <c r="N72" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="N72" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="O72" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P72" s="1"/>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="G73" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J73" s="1" t="s">
+      <c r="K73" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="L73" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="L73" s="1" t="s">
+      <c r="M73" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="M73" s="1" t="s">
+      <c r="N73" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="N73" s="1" t="s">
-        <v>604</v>
-      </c>
       <c r="O73" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P73" s="1"/>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="H74" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J74" s="1" t="s">
+      <c r="K74" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="L74" s="1" t="s">
+      <c r="M74" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="N74" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="M74" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="N74" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="O74" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P74" s="1"/>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J75" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J75" s="1" t="s">
+      <c r="K75" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="L75" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="M75" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="L75" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="M75" s="1" t="s">
+      <c r="N75" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="N75" s="1" t="s">
-        <v>619</v>
-      </c>
       <c r="O75" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P75" s="1"/>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F76" s="1" t="s">
+      <c r="G76" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J76" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="L76" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="L76" s="1" t="s">
+      <c r="M76" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="N76" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="N76" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="O76" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P76" s="1"/>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F77" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="H77" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J77" s="1" t="s">
+      <c r="K77" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="L77" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="K77" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="L77" s="1" t="s">
+      <c r="M77" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="N77" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="M77" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="O77" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P77" s="1"/>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G78" s="1" t="s">
+      <c r="H78" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="H78" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J78" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="L78" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="M78" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="N78" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="N78" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="O78" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P78" s="1"/>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="D79" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F79" s="1" t="s">
+      <c r="G79" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="H79" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="M79" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="M79" s="1" t="s">
+      <c r="N79" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="N79" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="O79" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P79" s="1"/>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F80" s="1" t="s">
+      <c r="G80" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J80" s="1" t="s">
+      <c r="K80" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M80" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="K80" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="L80" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="M80" s="1" t="s">
+      <c r="N80" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="N80" s="1" t="s">
-        <v>654</v>
-      </c>
       <c r="O80" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P80" s="1"/>
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F81" s="1" t="s">
+      <c r="G81" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="H81" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J81" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J81" s="1" t="s">
+      <c r="K81" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L81" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="K81" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="L81" s="1" t="s">
+      <c r="M81" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="M81" s="1" t="s">
-        <v>661</v>
-      </c>
       <c r="N81" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P81" s="1"/>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F82" s="1" t="s">
+      <c r="G82" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="G82" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J82" s="1" t="s">
+      <c r="K82" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="L82" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="M82" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="L82" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="M82" s="1" t="s">
+      <c r="N82" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="N82" s="1" t="s">
-        <v>668</v>
-      </c>
       <c r="O82" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P82" s="1"/>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J83" s="1" t="s">
+      <c r="K83" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="L83" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="L83" s="1" t="s">
+      <c r="M83" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="M83" s="1" t="s">
+      <c r="N83" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="N83" s="1" t="s">
-        <v>675</v>
-      </c>
       <c r="O83" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P83" s="1"/>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F84" s="1" t="s">
+      <c r="G84" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J84" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="G84" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J84" s="1" t="s">
+      <c r="K84" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="M84" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="M84" s="1" t="s">
+      <c r="N84" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N84" s="1" t="s">
-        <v>681</v>
-      </c>
       <c r="O84" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P84" s="1"/>
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G85" s="1" t="s">
+      <c r="H85" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J85" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J85" s="1" t="s">
+      <c r="K85" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="L85" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="L85" s="1" t="s">
+      <c r="M85" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="M85" s="1" t="s">
+      <c r="N85" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="N85" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="O85" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P85" s="1"/>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F86" s="1" t="s">
+      <c r="G86" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="M86" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="M86" s="1" t="s">
+      <c r="N86" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="N86" s="1" t="s">
-        <v>693</v>
-      </c>
       <c r="O86" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P86" s="1"/>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F87" s="1" t="s">
+      <c r="G87" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="H87" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J87" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J87" s="1" t="s">
+      <c r="K87" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="L87" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="L87" s="1" t="s">
+      <c r="M87" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="M87" s="1" t="s">
+      <c r="N87" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="N87" s="1" t="s">
-        <v>702</v>
-      </c>
       <c r="O87" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P87" s="1"/>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F88" s="1" t="s">
+      <c r="G88" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="G88" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J88" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="L88" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="L88" s="1" t="s">
+      <c r="M88" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="M88" s="1" t="s">
+      <c r="N88" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="N88" s="1" t="s">
-        <v>710</v>
-      </c>
       <c r="O88" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P88" s="1"/>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F89" s="1" t="s">
+      <c r="G89" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="G89" s="1" t="s">
+      <c r="H89" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J89" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J89" s="1" t="s">
+      <c r="K89" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="K89" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L89" s="1" t="s">
+      <c r="M89" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="M89" s="1" t="s">
+      <c r="N89" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="N89" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="O89" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P89" s="1"/>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="D90" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F90" s="1" t="s">
+      <c r="G90" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="G90" s="1" t="s">
+      <c r="H90" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="I90" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="I90" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J90" s="1" t="s">
+      <c r="K90" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="L90" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="L90" s="1" t="s">
+      <c r="M90" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="N90" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="M90" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="N90" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="O90" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P90" s="1"/>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F91" s="1" t="s">
+      <c r="G91" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="H91" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="M91" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="M91" s="1" t="s">
+      <c r="N91" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="N91" s="1" t="s">
-        <v>732</v>
-      </c>
       <c r="O91" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P91" s="1"/>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F92" s="1" t="s">
+      <c r="G92" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J92" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J92" s="1" t="s">
+      <c r="K92" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="L92" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="L92" s="1" t="s">
+      <c r="M92" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="M92" s="1" t="s">
+      <c r="N92" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="N92" s="1" t="s">
-        <v>740</v>
-      </c>
       <c r="O92" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P92" s="1"/>
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F93" s="1" t="s">
+      <c r="G93" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J93" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="G93" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J93" s="1" t="s">
+      <c r="K93" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="L93" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="L93" s="1" t="s">
+      <c r="M93" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="M93" s="1" t="s">
+      <c r="N93" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="N93" s="1" t="s">
-        <v>748</v>
-      </c>
       <c r="O93" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P93" s="1"/>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F94" s="1" t="s">
+      <c r="G94" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="H94" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J94" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="H94" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J94" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="L94" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="N94" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="L94" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>755</v>
-      </c>
       <c r="O94" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P94" s="1"/>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G95" s="1" t="s">
+      <c r="H95" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J95" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J95" s="1" t="s">
+      <c r="K95" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="L95" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K95" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="L95" s="1" t="s">
+      <c r="M95" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="M95" s="1" t="s">
+      <c r="N95" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="N95" s="1" t="s">
-        <v>762</v>
-      </c>
       <c r="O95" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P95" s="1"/>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F96" s="1" t="s">
+      <c r="G96" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="H96" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J96" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J96" s="1" t="s">
+      <c r="K96" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="L96" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="L96" s="1" t="s">
+      <c r="M96" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="M96" s="1" t="s">
-        <v>770</v>
-      </c>
       <c r="N96" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P96" s="1"/>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F97" s="1" t="s">
+      <c r="G97" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="H97" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J97" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J97" s="1" t="s">
+      <c r="K97" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="L97" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="K97" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="L97" s="1" t="s">
+      <c r="M97" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="M97" s="1" t="s">
+      <c r="N97" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="N97" s="1" t="s">
-        <v>778</v>
-      </c>
       <c r="O97" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P97" s="1"/>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F98" s="1" t="s">
+      <c r="G98" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J98" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="G98" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J98" s="1" t="s">
+      <c r="K98" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="K98" s="1" t="s">
+      <c r="L98" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="M98" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="L98" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="M98" s="1" t="s">
+      <c r="N98" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="N98" s="1" t="s">
-        <v>785</v>
-      </c>
       <c r="O98" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P98" s="1"/>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J99" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J99" s="1" t="s">
+      <c r="K99" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="K99" s="1" t="s">
+      <c r="L99" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="L99" s="1" t="s">
+      <c r="M99" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="M99" s="1" t="s">
+      <c r="N99" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="N99" s="1" t="s">
-        <v>792</v>
-      </c>
       <c r="O99" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P99" s="1"/>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="D100" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F100" s="1" t="s">
+      <c r="G100" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J100" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J100" s="1" t="s">
+      <c r="K100" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="K100" s="1" t="s">
+      <c r="L100" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="L100" s="1" t="s">
+      <c r="M100" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="M100" s="1" t="s">
+      <c r="N100" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="N100" s="1" t="s">
-        <v>800</v>
-      </c>
       <c r="O100" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P100" s="1"/>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F101" s="1" t="s">
+      <c r="G101" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H101" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="H101" s="1" t="s">
+      <c r="I101" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J101" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J101" s="1" t="s">
+      <c r="K101" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="L101" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="L101" s="1" t="s">
+      <c r="M101" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="M101" s="1" t="s">
+      <c r="N101" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="N101" s="1" t="s">
-        <v>809</v>
-      </c>
       <c r="O101" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P101" s="1"/>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F102" s="1" t="s">
+      <c r="G102" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="G102" s="1" t="s">
+      <c r="H102" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J102" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="H102" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J102" s="1" t="s">
+      <c r="K102" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="L102" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="K102" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="L102" s="1" t="s">
+      <c r="M102" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="M102" s="1" t="s">
+      <c r="N102" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="N102" s="1" t="s">
-        <v>817</v>
-      </c>
       <c r="O102" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P102" s="1"/>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F103" s="1" t="s">
+      <c r="G103" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J103" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="G103" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J103" s="1" t="s">
+      <c r="K103" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="L103" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="L103" s="1" t="s">
+      <c r="M103" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="M103" s="1" t="s">
+      <c r="N103" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="N103" s="1" t="s">
-        <v>824</v>
-      </c>
       <c r="O103" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P103" s="1"/>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="D104" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F104" s="1" t="s">
+      <c r="G104" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="H104" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J104" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J104" s="1" t="s">
+      <c r="K104" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="L104" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="L104" s="1" t="s">
+      <c r="M104" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="M104" s="1" t="s">
+      <c r="N104" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="N104" s="1" t="s">
-        <v>833</v>
-      </c>
       <c r="O104" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P104" s="1"/>
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G105" s="1" t="s">
+      <c r="H105" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J105" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J105" s="1" t="s">
+      <c r="K105" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="L105" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="M105" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="L105" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="M105" s="1" t="s">
+      <c r="N105" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="N105" s="1" t="s">
-        <v>840</v>
-      </c>
       <c r="O105" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P105" s="1"/>
     </row>
     <row r="106" spans="1:16">
       <c r="A106" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="D106" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F106" s="1" t="s">
+      <c r="G106" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J106" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J106" s="1" t="s">
+      <c r="K106" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="K106" s="1" t="s">
+      <c r="L106" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="M106" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="L106" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="M106" s="1" t="s">
+      <c r="N106" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="N106" s="1" t="s">
-        <v>847</v>
-      </c>
       <c r="O106" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P106" s="1"/>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F107" s="1" t="s">
+      <c r="G107" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="G107" s="1" t="s">
+      <c r="H107" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J107" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J107" s="1" t="s">
+      <c r="K107" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="L107" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="K107" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="L107" s="1" t="s">
+      <c r="M107" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="N107" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="M107" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="N107" s="1" t="s">
-        <v>854</v>
-      </c>
       <c r="O107" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P107" s="1"/>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J108" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J108" s="1" t="s">
+      <c r="K108" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="K108" s="1" t="s">
+      <c r="L108" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="L108" s="1" t="s">
+      <c r="M108" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="N108" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="M108" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="N108" s="1" t="s">
-        <v>860</v>
-      </c>
       <c r="O108" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P108" s="1"/>
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F109" s="1" t="s">
+      <c r="G109" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="G109" s="1" t="s">
+      <c r="H109" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J109" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="H109" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J109" s="1" t="s">
+      <c r="K109" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="M109" s="1" t="s">
         <v>865</v>
       </c>
-      <c r="K109" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="M109" s="1" t="s">
+      <c r="N109" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="N109" s="1" t="s">
-        <v>867</v>
-      </c>
       <c r="O109" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P109" s="1"/>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F110" s="1" t="s">
+      <c r="G110" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J110" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="G110" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J110" s="1" t="s">
+      <c r="K110" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L110" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="K110" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L110" s="1" t="s">
+      <c r="M110" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="N110" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="M110" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="N110" s="1" t="s">
-        <v>873</v>
-      </c>
       <c r="O110" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P110" s="1"/>
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F111" s="1" t="s">
+      <c r="G111" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J111" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="G111" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J111" s="1" t="s">
+      <c r="K111" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="L111" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="K111" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="L111" s="1" t="s">
+      <c r="M111" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="M111" s="1" t="s">
+      <c r="N111" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="N111" s="1" t="s">
-        <v>880</v>
-      </c>
       <c r="O111" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P111" s="1"/>
     </row>
     <row r="112" spans="1:16">
       <c r="A112" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F112" s="1" t="s">
+      <c r="G112" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="G112" s="1" t="s">
+      <c r="H112" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J112" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="H112" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J112" s="1" t="s">
+      <c r="K112" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M112" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="K112" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L112" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="M112" s="1" t="s">
+      <c r="N112" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="N112" s="1" t="s">
-        <v>887</v>
-      </c>
       <c r="O112" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P112" s="1"/>
     </row>
     <row r="113" spans="1:16">
       <c r="A113" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="K113" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="D113" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="K113" s="1" t="s">
+      <c r="L113" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="L113" s="1" t="s">
+      <c r="M113" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="M113" s="1" t="s">
+      <c r="N113" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="N113" s="1" t="s">
-        <v>893</v>
-      </c>
       <c r="O113" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P113" s="1"/>
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F114" s="1" t="s">
+      <c r="G114" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="G114" s="1" t="s">
+      <c r="H114" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J114" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="H114" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J114" s="1" t="s">
+      <c r="K114" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L114" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="K114" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L114" s="1" t="s">
+      <c r="M114" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="M114" s="1" t="s">
+      <c r="N114" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="N114" s="1" t="s">
-        <v>901</v>
-      </c>
       <c r="O114" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P114" s="1"/>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F115" s="1" t="s">
+      <c r="G115" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="H115" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J115" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="H115" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J115" s="1" t="s">
+      <c r="K115" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="M115" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="K115" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="M115" s="1" t="s">
+      <c r="N115" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="N115" s="1" t="s">
-        <v>908</v>
-      </c>
       <c r="O115" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P115" s="1"/>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F116" s="1" t="s">
+      <c r="G116" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="G116" s="1" t="s">
+      <c r="H116" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J116" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J116" s="1" t="s">
+      <c r="K116" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="L116" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="K116" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="L116" s="1" t="s">
+      <c r="M116" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="M116" s="1" t="s">
+      <c r="N116" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="N116" s="1" t="s">
-        <v>916</v>
-      </c>
       <c r="O116" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P116" s="1"/>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G117" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="G117" s="1" t="s">
+      <c r="H117" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="H117" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J117" s="1" t="s">
+      <c r="K117" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L117" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="K117" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L117" s="1" t="s">
+      <c r="M117" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="M117" s="1" t="s">
+      <c r="N117" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="N117" s="1" t="s">
-        <v>923</v>
-      </c>
       <c r="O117" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P117" s="1"/>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="D118" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F118" s="1" t="s">
+      <c r="G118" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="H118" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="K118" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="H118" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="K118" s="1" t="s">
+      <c r="L118" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="M118" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="L118" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="M118" s="1" t="s">
+      <c r="N118" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="N118" s="1" t="s">
-        <v>930</v>
-      </c>
       <c r="O118" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P118" s="1"/>
     </row>
     <row r="119" spans="1:16">
       <c r="A119" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F119" s="1" t="s">
+      <c r="G119" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J119" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="G119" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J119" s="1" t="s">
+      <c r="K119" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="M119" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="K119" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="L119" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="M119" s="1" t="s">
+      <c r="N119" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="N119" s="1" t="s">
-        <v>936</v>
-      </c>
       <c r="O119" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P119" s="1"/>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F120" s="1" t="s">
+      <c r="G120" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J120" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="G120" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J120" s="1" t="s">
+      <c r="K120" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="K120" s="1" t="s">
+      <c r="L120" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="M120" s="1" t="s">
         <v>941</v>
       </c>
-      <c r="L120" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="M120" s="1" t="s">
+      <c r="N120" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="N120" s="1" t="s">
-        <v>943</v>
-      </c>
       <c r="O120" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P120" s="1"/>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F121" s="1" t="s">
+      <c r="G121" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="G121" s="1" t="s">
+      <c r="H121" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J121" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="H121" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J121" s="1" t="s">
+      <c r="K121" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="K121" s="1" t="s">
+      <c r="L121" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="L121" s="1" t="s">
+      <c r="M121" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="M121" s="1" t="s">
+      <c r="N121" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="N121" s="1" t="s">
-        <v>952</v>
-      </c>
       <c r="O121" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P121" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>